--- a/part.xlsx
+++ b/part.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hkmccloud-my.sharepoint.com/personal/yeo19_hyundai_com/Documents/업무/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{50B47978-6339-4B3E-8859-401D644D4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A292F56-E3BD-41AE-AB2A-7060E30347BA}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{50B47978-6339-4B3E-8859-401D644D4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A28C0EB9-4BCB-4CD0-B8A7-3549F988483B}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99FC48C-34FE-434E-80D7-4E5AAE265EBA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="1940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="1942">
   <si>
     <t>자재번호</t>
   </si>
@@ -5956,6 +5956,14 @@
   </si>
   <si>
     <t>3-3 4단6열</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13100-10001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3-3 6단 5열</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6063,7 +6071,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6098,6 +6106,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6452,7 +6463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD56D84-AAB8-4F28-8C6E-523199CE1743}">
-  <dimension ref="A1:G970"/>
+  <dimension ref="A1:G971"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
@@ -14220,9 +14231,17 @@
         <v>1939</v>
       </c>
     </row>
+    <row r="971" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A971" s="12" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B971" s="3" t="s">
+        <v>1941</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A864:B943 A1 A2:B846 A847:A848 A944:A970">
+  <conditionalFormatting sqref="A864:B943 A1 A2:B846 A847:A848 A944:A971">
     <cfRule type="duplicateValues" dxfId="1" priority="7" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">

--- a/part.xlsx
+++ b/part.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hkmccloud-my.sharepoint.com/personal/yeo19_hyundai_com/Documents/업무/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="82" documentId="13_ncr:1_{50B47978-6339-4B3E-8859-401D644D4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30ACE933-CA83-49A7-BB44-8E55E3F04427}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{50B47978-6339-4B3E-8859-401D644D4F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C5CFCC4-B6CD-4A76-8D58-FB142B1CABE4}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F99FC48C-34FE-434E-80D7-4E5AAE265EBA}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$971</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$B$970</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1940" uniqueCount="1935">
   <si>
     <t>자재번호</t>
   </si>
@@ -2585,9 +2585,6 @@
     <t>1-3 2단1열</t>
   </si>
   <si>
-    <t>1-3 2단2열</t>
-  </si>
-  <si>
     <t>1-3 2단3열</t>
   </si>
   <si>
@@ -5915,10 +5912,6 @@
   </si>
   <si>
     <t>11653-12056ka</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>11425-06167p</t>
@@ -6429,7 +6422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD56D84-AAB8-4F28-8C6E-523199CE1743}">
-  <dimension ref="A1:F971"/>
+  <dimension ref="A1:F970"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.125" bestFit="1" customWidth="1"/>
@@ -6638,7 +6631,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>763</v>
@@ -6670,7 +6663,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>767</v>
@@ -6734,7 +6727,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>775</v>
@@ -6758,7 +6751,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>778</v>
@@ -6766,7 +6759,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>779</v>
@@ -6790,7 +6783,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>782</v>
@@ -6814,7 +6807,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>785</v>
@@ -6830,7 +6823,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>787</v>
@@ -6838,7 +6831,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>788</v>
@@ -6934,7 +6927,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>800</v>
@@ -6950,7 +6943,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>802</v>
@@ -6990,7 +6983,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>807</v>
@@ -7062,7 +7055,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>816</v>
@@ -7102,7 +7095,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>1931</v>
+        <v>71</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>821</v>
@@ -7110,7 +7103,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>822</v>
@@ -7118,7 +7111,7 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>823</v>
@@ -7126,7 +7119,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>73</v>
+        <v>1789</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>824</v>
@@ -7142,7 +7135,7 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>1791</v>
+        <v>74</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>826</v>
@@ -7150,7 +7143,7 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>74</v>
+        <v>1791</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>827</v>
@@ -7158,7 +7151,7 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>1792</v>
+        <v>75</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>828</v>
@@ -7166,7 +7159,7 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>75</v>
+        <v>1792</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>829</v>
@@ -7174,7 +7167,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>1793</v>
+        <v>76</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>830</v>
@@ -7182,7 +7175,7 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>76</v>
+        <v>1793</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>831</v>
@@ -7190,7 +7183,7 @@
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>1794</v>
+        <v>77</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>832</v>
@@ -7198,7 +7191,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>77</v>
+        <v>1794</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>833</v>
@@ -7206,7 +7199,7 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>1795</v>
+        <v>78</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>834</v>
@@ -7214,7 +7207,7 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>835</v>
@@ -7222,7 +7215,7 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>79</v>
+        <v>1795</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>836</v>
@@ -7238,7 +7231,7 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>1797</v>
+        <v>80</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>838</v>
@@ -7246,7 +7239,7 @@
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>839</v>
@@ -7254,7 +7247,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>840</v>
@@ -7262,7 +7255,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>82</v>
+        <v>1673</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>841</v>
@@ -7270,7 +7263,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>1674</v>
+        <v>1797</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>842</v>
@@ -7278,7 +7271,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>1798</v>
+        <v>83</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>843</v>
@@ -7286,7 +7279,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>83</v>
+        <v>1798</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>844</v>
@@ -7294,7 +7287,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>1799</v>
+        <v>84</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>845</v>
@@ -7302,7 +7295,7 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>846</v>
@@ -7310,7 +7303,7 @@
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>85</v>
+        <v>1799</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>847</v>
@@ -7318,7 +7311,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>1800</v>
+        <v>86</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>848</v>
@@ -7326,7 +7319,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>849</v>
@@ -7334,7 +7327,7 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>87</v>
+        <v>1800</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>850</v>
@@ -7350,7 +7343,7 @@
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>1802</v>
+        <v>88</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>852</v>
@@ -7358,7 +7351,7 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>853</v>
@@ -7366,7 +7359,7 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>89</v>
+        <v>1802</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>854</v>
@@ -7374,7 +7367,7 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>1803</v>
+        <v>90</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>855</v>
@@ -7382,7 +7375,7 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>90</v>
+        <v>1803</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>856</v>
@@ -7398,7 +7391,7 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>1805</v>
+        <v>91</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>858</v>
@@ -7406,7 +7399,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>91</v>
+        <v>1805</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>859</v>
@@ -7422,7 +7415,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>1807</v>
+        <v>92</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>861</v>
@@ -7430,7 +7423,7 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>862</v>
@@ -7438,7 +7431,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>863</v>
@@ -7446,7 +7439,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>864</v>
@@ -7454,7 +7447,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>865</v>
@@ -7462,7 +7455,7 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>866</v>
@@ -7470,7 +7463,7 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>867</v>
@@ -7478,7 +7471,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>868</v>
@@ -7486,7 +7479,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>869</v>
@@ -7494,7 +7487,7 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>870</v>
@@ -7502,7 +7495,7 @@
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>101</v>
+        <v>1807</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>871</v>
@@ -7510,7 +7503,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>1808</v>
+        <v>102</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>872</v>
@@ -7518,7 +7511,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>873</v>
@@ -7526,7 +7519,7 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>103</v>
+        <v>1808</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>874</v>
@@ -7534,7 +7527,7 @@
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>1809</v>
+        <v>104</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>875</v>
@@ -7542,7 +7535,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>876</v>
@@ -7550,7 +7543,7 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>877</v>
@@ -7558,7 +7551,7 @@
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>878</v>
@@ -7566,7 +7559,7 @@
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>879</v>
@@ -7574,7 +7567,7 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>880</v>
@@ -7582,7 +7575,7 @@
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>881</v>
@@ -7590,7 +7583,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>882</v>
@@ -7598,7 +7591,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>883</v>
@@ -7606,7 +7599,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>884</v>
@@ -7614,7 +7607,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>885</v>
@@ -7622,7 +7615,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>886</v>
@@ -7630,7 +7623,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>887</v>
@@ -7638,7 +7631,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>888</v>
@@ -7646,7 +7639,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>889</v>
@@ -7654,7 +7647,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>118</v>
+        <v>1809</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>890</v>
@@ -7662,7 +7655,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>1810</v>
+        <v>119</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>891</v>
@@ -7670,7 +7663,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>892</v>
@@ -7678,7 +7671,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>893</v>
@@ -7686,7 +7679,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>894</v>
@@ -7694,7 +7687,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>122</v>
+        <v>1810</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>895</v>
@@ -7702,7 +7695,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>1811</v>
+        <v>123</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>896</v>
@@ -7710,7 +7703,7 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>123</v>
+        <v>1811</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>897</v>
@@ -7718,7 +7711,7 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>1812</v>
+        <v>124</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>898</v>
@@ -7726,7 +7719,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>124</v>
+        <v>1812</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>899</v>
@@ -7734,7 +7727,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>1813</v>
+        <v>125</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>900</v>
@@ -7742,7 +7735,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>125</v>
+        <v>1813</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>901</v>
@@ -7750,7 +7743,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>1814</v>
+        <v>126</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>902</v>
@@ -7758,7 +7751,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>903</v>
@@ -7766,7 +7759,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>904</v>
@@ -7774,7 +7767,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>905</v>
@@ -7782,7 +7775,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>906</v>
@@ -7790,7 +7783,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>130</v>
+        <v>1814</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>907</v>
@@ -7798,7 +7791,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>1815</v>
+        <v>131</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>908</v>
@@ -7806,7 +7799,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>909</v>
@@ -7814,7 +7807,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>910</v>
@@ -7822,7 +7815,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>911</v>
@@ -7830,7 +7823,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>912</v>
@@ -7838,7 +7831,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>913</v>
@@ -7846,7 +7839,7 @@
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>914</v>
@@ -7854,7 +7847,7 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>915</v>
@@ -7862,7 +7855,7 @@
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>916</v>
@@ -7870,7 +7863,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>917</v>
@@ -7878,7 +7871,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>918</v>
@@ -7886,7 +7879,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>919</v>
@@ -7894,7 +7887,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>920</v>
@@ -7902,7 +7895,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>921</v>
@@ -7910,7 +7903,7 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>922</v>
@@ -7918,7 +7911,7 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>923</v>
@@ -7926,7 +7919,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>924</v>
@@ -7934,7 +7927,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>925</v>
@@ -7942,7 +7935,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>926</v>
@@ -7950,7 +7943,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>927</v>
@@ -7958,7 +7951,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>928</v>
@@ -7966,7 +7959,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>929</v>
@@ -7974,7 +7967,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>152</v>
+        <v>1815</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>930</v>
@@ -7982,7 +7975,7 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>1816</v>
+        <v>153</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>931</v>
@@ -7990,7 +7983,7 @@
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>153</v>
+        <v>1816</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>932</v>
@@ -7998,7 +7991,7 @@
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>1817</v>
+        <v>154</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>933</v>
@@ -8006,7 +7999,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>934</v>
@@ -8014,7 +8007,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>935</v>
@@ -8022,7 +8015,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>936</v>
@@ -8030,7 +8023,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>937</v>
@@ -8038,7 +8031,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>158</v>
+        <v>1674</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>938</v>
@@ -8046,7 +8039,7 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>1675</v>
+        <v>1817</v>
       </c>
       <c r="B202" s="3" t="s">
         <v>939</v>
@@ -8054,7 +8047,7 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>1818</v>
+        <v>1675</v>
       </c>
       <c r="B203" s="3" t="s">
         <v>940</v>
@@ -8062,7 +8055,7 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>1676</v>
+        <v>1765</v>
       </c>
       <c r="B204" s="3" t="s">
         <v>941</v>
@@ -8070,7 +8063,7 @@
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>1766</v>
+        <v>1818</v>
       </c>
       <c r="B205" s="3" t="s">
         <v>942</v>
@@ -8086,7 +8079,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>1820</v>
+        <v>159</v>
       </c>
       <c r="B207" s="3" t="s">
         <v>944</v>
@@ -8094,7 +8087,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>159</v>
+        <v>1676</v>
       </c>
       <c r="B208" s="3" t="s">
         <v>945</v>
@@ -8102,7 +8095,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>1677</v>
+        <v>1820</v>
       </c>
       <c r="B209" s="3" t="s">
         <v>946</v>
@@ -8110,7 +8103,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>1821</v>
+        <v>160</v>
       </c>
       <c r="B210" s="3" t="s">
         <v>947</v>
@@ -8118,7 +8111,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>160</v>
+        <v>1821</v>
       </c>
       <c r="B211" s="3" t="s">
         <v>948</v>
@@ -8126,7 +8119,7 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>1822</v>
+        <v>161</v>
       </c>
       <c r="B212" s="3" t="s">
         <v>949</v>
@@ -8134,7 +8127,7 @@
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>161</v>
+        <v>1677</v>
       </c>
       <c r="B213" s="3" t="s">
         <v>950</v>
@@ -8142,7 +8135,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>1678</v>
+        <v>1822</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>951</v>
@@ -8150,7 +8143,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>1823</v>
+        <v>162</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>952</v>
@@ -8158,7 +8151,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>953</v>
@@ -8166,7 +8159,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>954</v>
@@ -8174,7 +8167,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>955</v>
@@ -8182,7 +8175,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B219" s="3" t="s">
         <v>956</v>
@@ -8190,7 +8183,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>957</v>
@@ -8198,7 +8191,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>958</v>
@@ -8206,7 +8199,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B222" s="3" t="s">
         <v>959</v>
@@ -8214,7 +8207,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B223" s="3" t="s">
         <v>960</v>
@@ -8222,7 +8215,7 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B224" s="3" t="s">
         <v>961</v>
@@ -8230,7 +8223,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B225" s="3" t="s">
         <v>962</v>
@@ -8238,7 +8231,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B226" s="3" t="s">
         <v>963</v>
@@ -8246,7 +8239,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B227" s="3" t="s">
         <v>964</v>
@@ -8254,7 +8247,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B228" s="3" t="s">
         <v>965</v>
@@ -8262,7 +8255,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B229" s="3" t="s">
         <v>966</v>
@@ -8270,7 +8263,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B230" s="3" t="s">
         <v>967</v>
@@ -8278,7 +8271,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B231" s="3" t="s">
         <v>968</v>
@@ -8286,7 +8279,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B232" s="3" t="s">
         <v>969</v>
@@ -8294,7 +8287,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B233" s="3" t="s">
         <v>970</v>
@@ -8302,7 +8295,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B234" s="3" t="s">
         <v>971</v>
@@ -8310,7 +8303,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B235" s="3" t="s">
         <v>972</v>
@@ -8318,7 +8311,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B236" s="3" t="s">
         <v>973</v>
@@ -8326,7 +8319,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B237" s="3" t="s">
         <v>974</v>
@@ -8334,7 +8327,7 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>975</v>
@@ -8342,7 +8335,7 @@
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B239" s="3" t="s">
         <v>976</v>
@@ -8350,7 +8343,7 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B240" s="3" t="s">
         <v>977</v>
@@ -8358,7 +8351,7 @@
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B241" s="3" t="s">
         <v>978</v>
@@ -8366,7 +8359,7 @@
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B242" s="3" t="s">
         <v>979</v>
@@ -8374,7 +8367,7 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B243" s="3" t="s">
         <v>980</v>
@@ -8382,7 +8375,7 @@
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B244" s="3" t="s">
         <v>981</v>
@@ -8390,7 +8383,7 @@
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B245" s="3" t="s">
         <v>982</v>
@@ -8398,7 +8391,7 @@
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B246" s="3" t="s">
         <v>983</v>
@@ -8406,7 +8399,7 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B247" s="3" t="s">
         <v>984</v>
@@ -8414,7 +8407,7 @@
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B248" s="3" t="s">
         <v>985</v>
@@ -8422,7 +8415,7 @@
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B249" s="3" t="s">
         <v>986</v>
@@ -8430,7 +8423,7 @@
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B250" s="3" t="s">
         <v>987</v>
@@ -8438,7 +8431,7 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B251" s="3" t="s">
         <v>988</v>
@@ -8446,7 +8439,7 @@
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B252" s="3" t="s">
         <v>989</v>
@@ -8454,7 +8447,7 @@
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>199</v>
+        <v>1678</v>
       </c>
       <c r="B253" s="3" t="s">
         <v>990</v>
@@ -8462,7 +8455,7 @@
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>1679</v>
+        <v>1823</v>
       </c>
       <c r="B254" s="3" t="s">
         <v>991</v>
@@ -8470,7 +8463,7 @@
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>1824</v>
+        <v>256</v>
       </c>
       <c r="B255" s="3" t="s">
         <v>992</v>
@@ -8478,7 +8471,7 @@
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B256" s="3" t="s">
         <v>993</v>
@@ -8486,7 +8479,7 @@
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B257" s="3" t="s">
         <v>994</v>
@@ -8494,7 +8487,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>258</v>
+        <v>1679</v>
       </c>
       <c r="B258" s="3" t="s">
         <v>995</v>
@@ -8502,7 +8495,7 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>1680</v>
+        <v>1824</v>
       </c>
       <c r="B259" s="3" t="s">
         <v>996</v>
@@ -8510,7 +8503,7 @@
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
-        <v>1825</v>
+        <v>1680</v>
       </c>
       <c r="B260" s="3" t="s">
         <v>997</v>
@@ -8518,7 +8511,7 @@
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>1681</v>
+        <v>1782</v>
       </c>
       <c r="B261" s="3" t="s">
         <v>998</v>
@@ -8526,7 +8519,7 @@
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
-        <v>1783</v>
+        <v>259</v>
       </c>
       <c r="B262" s="3" t="s">
         <v>999</v>
@@ -8534,7 +8527,7 @@
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>259</v>
+        <v>1825</v>
       </c>
       <c r="B263" s="3" t="s">
         <v>1000</v>
@@ -8542,7 +8535,7 @@
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>1826</v>
+        <v>1681</v>
       </c>
       <c r="B264" s="3" t="s">
         <v>1001</v>
@@ -8550,7 +8543,7 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>1682</v>
+        <v>1766</v>
       </c>
       <c r="B265" s="3" t="s">
         <v>1002</v>
@@ -8598,7 +8591,7 @@
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>1772</v>
+        <v>260</v>
       </c>
       <c r="B271" s="3" t="s">
         <v>1008</v>
@@ -8606,7 +8599,7 @@
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>260</v>
+        <v>1682</v>
       </c>
       <c r="B272" s="3" t="s">
         <v>1009</v>
@@ -8614,7 +8607,7 @@
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>1683</v>
+        <v>261</v>
       </c>
       <c r="B273" s="3" t="s">
         <v>1010</v>
@@ -8622,7 +8615,7 @@
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>261</v>
+        <v>1683</v>
       </c>
       <c r="B274" s="3" t="s">
         <v>1011</v>
@@ -8630,7 +8623,7 @@
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>1684</v>
+        <v>1826</v>
       </c>
       <c r="B275" s="3" t="s">
         <v>1012</v>
@@ -8638,7 +8631,7 @@
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
-        <v>1827</v>
+        <v>262</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>1013</v>
@@ -8646,7 +8639,7 @@
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>262</v>
+        <v>1684</v>
       </c>
       <c r="B277" s="3" t="s">
         <v>1014</v>
@@ -8670,7 +8663,7 @@
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>1687</v>
+        <v>1827</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>1017</v>
@@ -8678,7 +8671,7 @@
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>1828</v>
+        <v>1687</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>1018</v>
@@ -8686,7 +8679,7 @@
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>1688</v>
+        <v>1828</v>
       </c>
       <c r="B282" s="3" t="s">
         <v>1019</v>
@@ -8694,7 +8687,7 @@
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>1829</v>
+        <v>263</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>1020</v>
@@ -8702,7 +8695,7 @@
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>263</v>
+        <v>1829</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>1021</v>
@@ -8710,7 +8703,7 @@
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>1830</v>
+        <v>264</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>1022</v>
@@ -8718,7 +8711,7 @@
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
-        <v>264</v>
+        <v>1688</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>1023</v>
@@ -8726,7 +8719,7 @@
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>1689</v>
+        <v>1830</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>1024</v>
@@ -8734,7 +8727,7 @@
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
-        <v>1831</v>
+        <v>1689</v>
       </c>
       <c r="B288" s="3" t="s">
         <v>1025</v>
@@ -8742,7 +8735,7 @@
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>1690</v>
+        <v>1831</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>1026</v>
@@ -8758,7 +8751,7 @@
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>1833</v>
+        <v>265</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>1028</v>
@@ -8766,7 +8759,7 @@
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
-        <v>265</v>
+        <v>1930</v>
       </c>
       <c r="B292" s="3" t="s">
         <v>1029</v>
@@ -8774,7 +8767,7 @@
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>1030</v>
@@ -8782,7 +8775,7 @@
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>1031</v>
@@ -8790,7 +8783,7 @@
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>1934</v>
+        <v>266</v>
       </c>
       <c r="B295" s="3" t="s">
         <v>1032</v>
@@ -8798,7 +8791,7 @@
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>1033</v>
@@ -8806,7 +8799,7 @@
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B297" s="3" t="s">
         <v>1034</v>
@@ -8814,7 +8807,7 @@
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>1035</v>
@@ -8822,7 +8815,7 @@
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>1036</v>
@@ -8830,7 +8823,7 @@
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
-        <v>270</v>
+        <v>1775</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>1037</v>
@@ -8838,7 +8831,7 @@
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>1776</v>
+        <v>271</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>1038</v>
@@ -8846,7 +8839,7 @@
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>1039</v>
@@ -8854,7 +8847,7 @@
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>1040</v>
@@ -8862,7 +8855,7 @@
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>1041</v>
@@ -8870,7 +8863,7 @@
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>1042</v>
@@ -8878,7 +8871,7 @@
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>1043</v>
@@ -8886,7 +8879,7 @@
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>1044</v>
@@ -8894,7 +8887,7 @@
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>1045</v>
@@ -8902,7 +8895,7 @@
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>1046</v>
@@ -8910,7 +8903,7 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>1047</v>
@@ -8918,7 +8911,7 @@
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>1048</v>
@@ -8926,7 +8919,7 @@
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
-        <v>281</v>
+        <v>1833</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>1049</v>
@@ -8934,7 +8927,7 @@
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>1834</v>
+        <v>282</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>1050</v>
@@ -8942,7 +8935,7 @@
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>1051</v>
@@ -8950,7 +8943,7 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>283</v>
+        <v>1834</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>1052</v>
@@ -8958,7 +8951,7 @@
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
-        <v>1835</v>
+        <v>284</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>1053</v>
@@ -8966,7 +8959,7 @@
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>1054</v>
@@ -8974,7 +8967,7 @@
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>1055</v>
@@ -8982,7 +8975,7 @@
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>1056</v>
@@ -8990,7 +8983,7 @@
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>1057</v>
@@ -8998,7 +8991,7 @@
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>1058</v>
@@ -9006,7 +8999,7 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
-        <v>289</v>
+        <v>1835</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>1059</v>
@@ -9014,7 +9007,7 @@
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>1836</v>
+        <v>290</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>1060</v>
@@ -9022,7 +9015,7 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
-        <v>290</v>
+        <v>1776</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>1061</v>
@@ -9030,7 +9023,7 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>1777</v>
+        <v>1836</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>1062</v>
@@ -9038,7 +9031,7 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
-        <v>1837</v>
+        <v>291</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>1063</v>
@@ -9046,7 +9039,7 @@
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>1064</v>
@@ -9054,7 +9047,7 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>1065</v>
@@ -9062,7 +9055,7 @@
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>1066</v>
@@ -9070,7 +9063,7 @@
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>1067</v>
@@ -9078,7 +9071,7 @@
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>295</v>
+        <v>1690</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>1068</v>
@@ -9086,7 +9079,7 @@
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
-        <v>1691</v>
+        <v>296</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>1069</v>
@@ -9094,7 +9087,7 @@
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>1070</v>
@@ -9102,7 +9095,7 @@
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>1071</v>
@@ -9110,7 +9103,7 @@
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>1072</v>
@@ -9118,7 +9111,7 @@
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>1073</v>
@@ -9126,7 +9119,7 @@
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>1074</v>
@@ -9134,7 +9127,7 @@
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>1075</v>
@@ -9142,7 +9135,7 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>1076</v>
@@ -9150,7 +9143,7 @@
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>1077</v>
@@ -9158,7 +9151,7 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>1078</v>
@@ -9166,7 +9159,7 @@
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>1079</v>
@@ -9174,7 +9167,7 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>1080</v>
@@ -9182,7 +9175,7 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
-        <v>307</v>
+        <v>1777</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>1081</v>
@@ -9190,7 +9183,7 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>1778</v>
+        <v>308</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>1082</v>
@@ -9198,7 +9191,7 @@
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>1083</v>
@@ -9206,7 +9199,7 @@
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>1084</v>
@@ -9214,7 +9207,7 @@
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>1085</v>
@@ -9222,7 +9215,7 @@
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>1086</v>
@@ -9230,7 +9223,7 @@
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
-        <v>312</v>
+        <v>1837</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>1087</v>
@@ -9238,7 +9231,7 @@
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>1838</v>
+        <v>313</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>1088</v>
@@ -9246,7 +9239,7 @@
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>1089</v>
@@ -9254,7 +9247,7 @@
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>314</v>
+        <v>1691</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>1090</v>
@@ -9262,7 +9255,7 @@
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
-        <v>1692</v>
+        <v>315</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>1091</v>
@@ -9270,7 +9263,7 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>1092</v>
@@ -9278,7 +9271,7 @@
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>1093</v>
@@ -9286,7 +9279,7 @@
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>1094</v>
@@ -9294,7 +9287,7 @@
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>1095</v>
@@ -9302,7 +9295,7 @@
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>1096</v>
@@ -9310,7 +9303,7 @@
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>1097</v>
@@ -9318,7 +9311,7 @@
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>1098</v>
@@ -9326,7 +9319,7 @@
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>1099</v>
@@ -9334,7 +9327,7 @@
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>1100</v>
@@ -9342,7 +9335,7 @@
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>1101</v>
@@ -9350,7 +9343,7 @@
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>1102</v>
@@ -9358,7 +9351,7 @@
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>1103</v>
@@ -9366,7 +9359,7 @@
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>1104</v>
@@ -9374,7 +9367,7 @@
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>1105</v>
@@ -9382,7 +9375,7 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>329</v>
+        <v>1692</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>1106</v>
@@ -9390,7 +9383,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
-        <v>1693</v>
+        <v>330</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>1107</v>
@@ -9398,7 +9391,7 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>1108</v>
@@ -9406,7 +9399,7 @@
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>1109</v>
@@ -9414,7 +9407,7 @@
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>1110</v>
@@ -9422,7 +9415,7 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>1111</v>
@@ -9430,7 +9423,7 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>1112</v>
@@ -9438,7 +9431,7 @@
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>1113</v>
@@ -9446,7 +9439,7 @@
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>1114</v>
@@ -9454,7 +9447,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>1115</v>
@@ -9462,7 +9455,7 @@
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>1116</v>
@@ -9470,7 +9463,7 @@
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>1117</v>
@@ -9478,7 +9471,7 @@
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>1118</v>
@@ -9486,7 +9479,7 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>1119</v>
@@ -9494,7 +9487,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>342</v>
+        <v>1693</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>1120</v>
@@ -9502,7 +9495,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>1694</v>
+        <v>343</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>1121</v>
@@ -9510,7 +9503,7 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>1122</v>
@@ -9518,7 +9511,7 @@
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
-        <v>344</v>
+        <v>1694</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>1123</v>
@@ -9526,7 +9519,7 @@
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>1695</v>
+        <v>345</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>1124</v>
@@ -9534,7 +9527,7 @@
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>1125</v>
@@ -9542,7 +9535,7 @@
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>346</v>
+        <v>1838</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>1126</v>
@@ -9550,7 +9543,7 @@
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>1839</v>
+        <v>347</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>1127</v>
@@ -9558,7 +9551,7 @@
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>347</v>
+        <v>1695</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>1128</v>
@@ -9566,7 +9559,7 @@
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>1696</v>
+        <v>348</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>1129</v>
@@ -9574,7 +9567,7 @@
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>348</v>
+        <v>1696</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>1130</v>
@@ -9582,7 +9575,7 @@
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>1697</v>
+        <v>349</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>1131</v>
@@ -9590,7 +9583,7 @@
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>349</v>
+        <v>1697</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>1132</v>
@@ -9598,7 +9591,7 @@
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>1698</v>
+        <v>350</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>1133</v>
@@ -9606,7 +9599,7 @@
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>1134</v>
@@ -9614,7 +9607,7 @@
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>351</v>
+        <v>1698</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>1135</v>
@@ -9622,7 +9615,7 @@
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>1699</v>
+        <v>1839</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>1136</v>
@@ -9630,7 +9623,7 @@
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>1840</v>
+        <v>1699</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>1137</v>
@@ -9638,7 +9631,7 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>1700</v>
+        <v>1840</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>1138</v>
@@ -9654,7 +9647,7 @@
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>1842</v>
+        <v>352</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>1140</v>
@@ -9662,7 +9655,7 @@
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>352</v>
+        <v>1700</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>1141</v>
@@ -9670,7 +9663,7 @@
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>1701</v>
+        <v>353</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>1142</v>
@@ -9678,7 +9671,7 @@
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>353</v>
+        <v>1701</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>1143</v>
@@ -9686,7 +9679,7 @@
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>1702</v>
+        <v>354</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>1144</v>
@@ -9694,7 +9687,7 @@
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>1145</v>
@@ -9702,7 +9695,7 @@
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>1146</v>
@@ -9710,7 +9703,7 @@
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>1147</v>
@@ -9718,7 +9711,7 @@
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>1148</v>
@@ -9726,7 +9719,7 @@
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>358</v>
+        <v>1842</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>1149</v>
@@ -9734,7 +9727,7 @@
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>1843</v>
+        <v>1702</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>1150</v>
@@ -9742,7 +9735,7 @@
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>1703</v>
+        <v>359</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>1151</v>
@@ -9750,7 +9743,7 @@
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>359</v>
+        <v>1703</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>1152</v>
@@ -9758,7 +9751,7 @@
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>1704</v>
+        <v>1843</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>1153</v>
@@ -9766,7 +9759,7 @@
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>1844</v>
+        <v>1704</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>1154</v>
@@ -9774,7 +9767,7 @@
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
-        <v>1705</v>
+        <v>360</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>1155</v>
@@ -9782,7 +9775,7 @@
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>1156</v>
@@ -9790,7 +9783,7 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
-        <v>361</v>
+        <v>1705</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>1157</v>
@@ -9798,7 +9791,7 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>1706</v>
+        <v>362</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>1158</v>
@@ -9806,7 +9799,7 @@
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>1159</v>
@@ -9814,7 +9807,7 @@
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>363</v>
+        <v>1706</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>1160</v>
@@ -9822,7 +9815,7 @@
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
-        <v>1707</v>
+        <v>1844</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>1161</v>
@@ -9830,7 +9823,7 @@
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>1845</v>
+        <v>364</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>1162</v>
@@ -9838,7 +9831,7 @@
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>1163</v>
@@ -9846,7 +9839,7 @@
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>1164</v>
@@ -9854,7 +9847,7 @@
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B428" s="3" t="s">
         <v>1165</v>
@@ -9862,7 +9855,7 @@
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B429" s="3" t="s">
         <v>1166</v>
@@ -9870,7 +9863,7 @@
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B430" s="3" t="s">
         <v>1167</v>
@@ -9878,7 +9871,7 @@
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="3" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B431" s="3" t="s">
         <v>1168</v>
@@ -9886,7 +9879,7 @@
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B432" s="3" t="s">
         <v>1169</v>
@@ -9894,7 +9887,7 @@
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>1170</v>
@@ -9902,7 +9895,7 @@
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>1171</v>
@@ -9910,7 +9903,7 @@
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>1172</v>
@@ -9918,7 +9911,7 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>1173</v>
@@ -9926,7 +9919,7 @@
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="3" t="s">
-        <v>375</v>
+        <v>1707</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>1174</v>
@@ -9934,7 +9927,7 @@
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" s="3" t="s">
-        <v>1708</v>
+        <v>376</v>
       </c>
       <c r="B438" s="3" t="s">
         <v>1175</v>
@@ -9942,7 +9935,7 @@
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="3" t="s">
-        <v>376</v>
+        <v>1845</v>
       </c>
       <c r="B439" s="3" t="s">
         <v>1176</v>
@@ -9950,7 +9943,7 @@
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="3" t="s">
-        <v>1846</v>
+        <v>377</v>
       </c>
       <c r="B440" s="3" t="s">
         <v>1177</v>
@@ -9958,7 +9951,7 @@
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B441" s="3" t="s">
         <v>1178</v>
@@ -9966,7 +9959,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="3" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>1179</v>
@@ -9974,7 +9967,7 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>1180</v>
@@ -9982,7 +9975,7 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>1181</v>
@@ -9990,7 +9983,7 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>1182</v>
@@ -9998,7 +9991,7 @@
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="3" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>1183</v>
@@ -10006,7 +9999,7 @@
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>1184</v>
@@ -10014,7 +10007,7 @@
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>1185</v>
@@ -10022,7 +10015,7 @@
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="3" t="s">
-        <v>385</v>
+        <v>1708</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>1186</v>
@@ -10030,7 +10023,7 @@
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="3" t="s">
-        <v>1709</v>
+        <v>386</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>1187</v>
@@ -10038,7 +10031,7 @@
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="3" t="s">
-        <v>386</v>
+        <v>1709</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>1188</v>
@@ -10046,7 +10039,7 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="3" t="s">
-        <v>1710</v>
+        <v>387</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>1189</v>
@@ -10054,7 +10047,7 @@
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>1190</v>
@@ -10062,7 +10055,7 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
-        <v>388</v>
+        <v>1846</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>1191</v>
@@ -10070,7 +10063,7 @@
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="3" t="s">
-        <v>1847</v>
+        <v>389</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>1192</v>
@@ -10078,7 +10071,7 @@
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>1193</v>
@@ -10086,7 +10079,7 @@
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>1194</v>
@@ -10094,7 +10087,7 @@
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>1195</v>
@@ -10102,7 +10095,7 @@
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" s="3" t="s">
-        <v>392</v>
+        <v>1710</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>1196</v>
@@ -10110,7 +10103,7 @@
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" s="3" t="s">
-        <v>1711</v>
+        <v>393</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>1197</v>
@@ -10118,7 +10111,7 @@
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>1198</v>
@@ -10126,7 +10119,7 @@
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>1199</v>
@@ -10134,7 +10127,7 @@
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>1200</v>
@@ -10142,7 +10135,7 @@
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>1201</v>
@@ -10150,7 +10143,7 @@
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>1202</v>
@@ -10158,7 +10151,7 @@
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" s="3" t="s">
-        <v>398</v>
+        <v>1711</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>1203</v>
@@ -10174,7 +10167,7 @@
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468" s="3" t="s">
-        <v>1713</v>
+        <v>399</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>1205</v>
@@ -10182,7 +10175,7 @@
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>1206</v>
@@ -10190,7 +10183,7 @@
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B470" s="3" t="s">
         <v>1207</v>
@@ -10198,7 +10191,7 @@
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471" s="3" t="s">
-        <v>401</v>
+        <v>1713</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>1208</v>
@@ -10206,7 +10199,7 @@
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472" s="3" t="s">
-        <v>1714</v>
+        <v>402</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>1209</v>
@@ -10214,7 +10207,7 @@
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
-        <v>402</v>
+        <v>1714</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>1210</v>
@@ -10222,7 +10215,7 @@
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" s="3" t="s">
-        <v>1715</v>
+        <v>1847</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>1211</v>
@@ -10230,7 +10223,7 @@
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" s="3" t="s">
-        <v>1848</v>
+        <v>1715</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>1212</v>
@@ -10238,7 +10231,7 @@
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" s="3" t="s">
-        <v>1716</v>
+        <v>403</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>1213</v>
@@ -10246,7 +10239,7 @@
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477" s="3" t="s">
-        <v>403</v>
+        <v>1848</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>1214</v>
@@ -10254,7 +10247,7 @@
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478" s="3" t="s">
-        <v>1849</v>
+        <v>404</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>1215</v>
@@ -10262,7 +10255,7 @@
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479" s="3" t="s">
-        <v>404</v>
+        <v>1716</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>1216</v>
@@ -10270,7 +10263,7 @@
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480" s="3" t="s">
-        <v>1717</v>
+        <v>1849</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>1217</v>
@@ -10286,7 +10279,7 @@
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" s="3" t="s">
-        <v>1851</v>
+        <v>405</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>1219</v>
@@ -10294,7 +10287,7 @@
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>1220</v>
@@ -10302,7 +10295,7 @@
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" s="3" t="s">
-        <v>406</v>
+        <v>1851</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>1221</v>
@@ -10310,7 +10303,7 @@
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485" s="3" t="s">
-        <v>1852</v>
+        <v>407</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>1222</v>
@@ -10318,7 +10311,7 @@
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>1223</v>
@@ -10326,7 +10319,7 @@
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>1224</v>
@@ -10334,7 +10327,7 @@
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" s="3" t="s">
-        <v>409</v>
+        <v>1852</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>1225</v>
@@ -10342,7 +10335,7 @@
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" s="3" t="s">
-        <v>1853</v>
+        <v>410</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>1226</v>
@@ -10350,7 +10343,7 @@
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>1227</v>
@@ -10358,7 +10351,7 @@
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491" s="3" t="s">
-        <v>411</v>
+        <v>1717</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>1228</v>
@@ -10366,7 +10359,7 @@
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" s="3" t="s">
-        <v>1718</v>
+        <v>412</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>1229</v>
@@ -10374,7 +10367,7 @@
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>1230</v>
@@ -10382,7 +10375,7 @@
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>1231</v>
@@ -10390,7 +10383,7 @@
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" s="3" t="s">
-        <v>414</v>
+        <v>1718</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>1232</v>
@@ -10398,7 +10391,7 @@
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496" s="3" t="s">
-        <v>1719</v>
+        <v>1853</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>1233</v>
@@ -10414,7 +10407,7 @@
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" s="3" t="s">
-        <v>1855</v>
+        <v>415</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>1235</v>
@@ -10422,7 +10415,7 @@
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" s="3" t="s">
-        <v>415</v>
+        <v>1719</v>
       </c>
       <c r="B499" s="3" t="s">
         <v>1236</v>
@@ -10430,7 +10423,7 @@
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" s="3" t="s">
-        <v>1720</v>
+        <v>416</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>1237</v>
@@ -10438,7 +10431,7 @@
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>1238</v>
@@ -10446,7 +10439,7 @@
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" s="3" t="s">
-        <v>417</v>
+        <v>1855</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>1239</v>
@@ -10454,7 +10447,7 @@
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" s="3" t="s">
-        <v>1856</v>
+        <v>418</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>1240</v>
@@ -10462,7 +10455,7 @@
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" s="3" t="s">
-        <v>418</v>
+        <v>1783</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>1241</v>
@@ -10470,7 +10463,7 @@
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" s="3" t="s">
-        <v>1784</v>
+        <v>419</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>1242</v>
@@ -10478,7 +10471,7 @@
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>1243</v>
@@ -10486,7 +10479,7 @@
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>1244</v>
@@ -10494,7 +10487,7 @@
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" s="3" t="s">
-        <v>421</v>
+        <v>1856</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>1245</v>
@@ -10502,7 +10495,7 @@
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" s="3" t="s">
-        <v>1857</v>
+        <v>422</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>1246</v>
@@ -10510,7 +10503,7 @@
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>1247</v>
@@ -10518,7 +10511,7 @@
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" s="3" t="s">
-        <v>423</v>
+        <v>1720</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>1248</v>
@@ -10526,7 +10519,7 @@
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" s="3" t="s">
-        <v>1721</v>
+        <v>1857</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>1249</v>
@@ -10534,7 +10527,7 @@
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" s="3" t="s">
-        <v>1858</v>
+        <v>1721</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>1250</v>
@@ -10542,7 +10535,7 @@
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" s="3" t="s">
-        <v>1722</v>
+        <v>424</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>1251</v>
@@ -10550,7 +10543,7 @@
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B515" s="3" t="s">
         <v>1252</v>
@@ -10558,7 +10551,7 @@
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B516" s="3" t="s">
         <v>1253</v>
@@ -10566,7 +10559,7 @@
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B517" s="3" t="s">
         <v>1254</v>
@@ -10574,7 +10567,7 @@
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B518" s="3" t="s">
         <v>1255</v>
@@ -10582,7 +10575,7 @@
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>1256</v>
@@ -10590,7 +10583,7 @@
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520" s="3" t="s">
-        <v>429</v>
+        <v>1722</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>1257</v>
@@ -10598,7 +10591,7 @@
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521" s="3" t="s">
-        <v>1723</v>
+        <v>430</v>
       </c>
       <c r="B521" s="3" t="s">
         <v>1258</v>
@@ -10606,7 +10599,7 @@
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" s="3" t="s">
-        <v>430</v>
+        <v>1858</v>
       </c>
       <c r="B522" s="3" t="s">
         <v>1259</v>
@@ -10622,7 +10615,7 @@
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" s="3" t="s">
-        <v>1860</v>
+        <v>431</v>
       </c>
       <c r="B524" s="3" t="s">
         <v>1261</v>
@@ -10630,7 +10623,7 @@
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B525" s="3" t="s">
         <v>1262</v>
@@ -10638,7 +10631,7 @@
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B526" s="3" t="s">
         <v>1263</v>
@@ -10646,7 +10639,7 @@
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B527" s="3" t="s">
         <v>1264</v>
@@ -10654,7 +10647,7 @@
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B528" s="3" t="s">
         <v>1265</v>
@@ -10662,7 +10655,7 @@
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B529" s="3" t="s">
         <v>1266</v>
@@ -10670,7 +10663,7 @@
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B530" s="3" t="s">
         <v>1267</v>
@@ -10678,7 +10671,7 @@
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>1268</v>
@@ -10686,7 +10679,7 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B532" s="3" t="s">
         <v>1269</v>
@@ -10694,7 +10687,7 @@
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B533" s="3" t="s">
         <v>1270</v>
@@ -10702,7 +10695,7 @@
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534" s="3" t="s">
-        <v>440</v>
+        <v>1723</v>
       </c>
       <c r="B534" s="3" t="s">
         <v>1271</v>
@@ -10710,7 +10703,7 @@
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535" s="3" t="s">
-        <v>1724</v>
+        <v>1860</v>
       </c>
       <c r="B535" s="3" t="s">
         <v>1272</v>
@@ -10718,7 +10711,7 @@
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536" s="3" t="s">
-        <v>1861</v>
+        <v>441</v>
       </c>
       <c r="B536" s="3" t="s">
         <v>1273</v>
@@ -10726,7 +10719,7 @@
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B537" s="3" t="s">
         <v>1274</v>
@@ -10734,7 +10727,7 @@
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B538" s="3" t="s">
         <v>1275</v>
@@ -10742,7 +10735,7 @@
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B539" s="3" t="s">
         <v>1276</v>
@@ -10750,7 +10743,7 @@
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B540" s="3" t="s">
         <v>1277</v>
@@ -10758,7 +10751,7 @@
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>1278</v>
@@ -10766,7 +10759,7 @@
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>1279</v>
@@ -10774,7 +10767,7 @@
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B543" s="3" t="s">
         <v>1280</v>
@@ -10782,7 +10775,7 @@
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B544" s="3" t="s">
         <v>1281</v>
@@ -10790,7 +10783,7 @@
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545" s="3" t="s">
-        <v>449</v>
+        <v>1724</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>1282</v>
@@ -10798,7 +10791,7 @@
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546" s="3" t="s">
-        <v>1725</v>
+        <v>450</v>
       </c>
       <c r="B546" s="3" t="s">
         <v>1283</v>
@@ -10806,7 +10799,7 @@
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A547" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B547" s="3" t="s">
         <v>1284</v>
@@ -10814,7 +10807,7 @@
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548" s="3" t="s">
-        <v>451</v>
+        <v>1725</v>
       </c>
       <c r="B548" s="3" t="s">
         <v>1285</v>
@@ -10822,7 +10815,7 @@
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549" s="3" t="s">
-        <v>1726</v>
+        <v>1861</v>
       </c>
       <c r="B549" s="3" t="s">
         <v>1286</v>
@@ -10830,7 +10823,7 @@
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550" s="3" t="s">
-        <v>1862</v>
+        <v>452</v>
       </c>
       <c r="B550" s="3" t="s">
         <v>1287</v>
@@ -10838,7 +10831,7 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B551" s="3" t="s">
         <v>1288</v>
@@ -10846,7 +10839,7 @@
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>1289</v>
@@ -10854,7 +10847,7 @@
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B553" s="3" t="s">
         <v>1290</v>
@@ -10862,7 +10855,7 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B554" s="3" t="s">
         <v>1291</v>
@@ -10870,7 +10863,7 @@
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B555" s="3" t="s">
         <v>1292</v>
@@ -10878,7 +10871,7 @@
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B556" s="3" t="s">
         <v>1293</v>
@@ -10886,7 +10879,7 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557" s="3" t="s">
-        <v>458</v>
+        <v>1862</v>
       </c>
       <c r="B557" s="3" t="s">
         <v>1294</v>
@@ -10894,7 +10887,7 @@
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558" s="3" t="s">
-        <v>1863</v>
+        <v>1726</v>
       </c>
       <c r="B558" s="3" t="s">
         <v>1295</v>
@@ -10902,7 +10895,7 @@
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559" s="3" t="s">
-        <v>1727</v>
+        <v>459</v>
       </c>
       <c r="B559" s="3" t="s">
         <v>1296</v>
@@ -10910,7 +10903,7 @@
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560" s="3" t="s">
-        <v>459</v>
+        <v>713</v>
       </c>
       <c r="B560" s="3" t="s">
         <v>1297</v>
@@ -10918,7 +10911,7 @@
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561" s="3" t="s">
-        <v>713</v>
+        <v>460</v>
       </c>
       <c r="B561" s="3" t="s">
         <v>1298</v>
@@ -10926,7 +10919,7 @@
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B562" s="3" t="s">
         <v>1299</v>
@@ -10934,7 +10927,7 @@
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>1300</v>
@@ -10942,7 +10935,7 @@
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B564" s="3" t="s">
         <v>1301</v>
@@ -10950,7 +10943,7 @@
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B565" s="3" t="s">
         <v>1302</v>
@@ -10958,7 +10951,7 @@
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B566" s="3" t="s">
         <v>1303</v>
@@ -10966,7 +10959,7 @@
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B567" s="3" t="s">
         <v>1304</v>
@@ -10974,7 +10967,7 @@
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B568" s="3" t="s">
         <v>1305</v>
@@ -10982,7 +10975,7 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B569" s="3" t="s">
         <v>1306</v>
@@ -10990,7 +10983,7 @@
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B570" s="3" t="s">
         <v>1307</v>
@@ -10998,7 +10991,7 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B571" s="3" t="s">
         <v>1308</v>
@@ -11006,7 +10999,7 @@
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572" s="3" t="s">
-        <v>470</v>
+        <v>1863</v>
       </c>
       <c r="B572" s="3" t="s">
         <v>1309</v>
@@ -11014,7 +11007,7 @@
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573" s="3" t="s">
-        <v>1864</v>
+        <v>471</v>
       </c>
       <c r="B573" s="3" t="s">
         <v>1310</v>
@@ -11022,7 +11015,7 @@
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B574" s="3" t="s">
         <v>1311</v>
@@ -11030,7 +11023,7 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B575" s="3" t="s">
         <v>1312</v>
@@ -11038,7 +11031,7 @@
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576" s="3" t="s">
-        <v>473</v>
+        <v>1864</v>
       </c>
       <c r="B576" s="3" t="s">
         <v>1313</v>
@@ -11046,7 +11039,7 @@
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577" s="3" t="s">
-        <v>1865</v>
+        <v>474</v>
       </c>
       <c r="B577" s="3" t="s">
         <v>1314</v>
@@ -11054,7 +11047,7 @@
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B578" s="3" t="s">
         <v>1315</v>
@@ -11062,7 +11055,7 @@
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B579" s="3" t="s">
         <v>1316</v>
@@ -11070,7 +11063,7 @@
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B580" s="3" t="s">
         <v>1317</v>
@@ -11078,7 +11071,7 @@
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B581" s="3" t="s">
         <v>1318</v>
@@ -11086,7 +11079,7 @@
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B582" s="3" t="s">
         <v>1319</v>
@@ -11094,7 +11087,7 @@
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B583" s="3" t="s">
         <v>1320</v>
@@ -11102,7 +11095,7 @@
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B584" s="3" t="s">
         <v>1321</v>
@@ -11110,7 +11103,7 @@
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B585" s="3" t="s">
         <v>1322</v>
@@ -11118,7 +11111,7 @@
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B586" s="3" t="s">
         <v>1323</v>
@@ -11126,7 +11119,7 @@
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B587" s="3" t="s">
         <v>1324</v>
@@ -11134,7 +11127,7 @@
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B588" s="3" t="s">
         <v>1325</v>
@@ -11142,7 +11135,7 @@
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B589" s="3" t="s">
         <v>1326</v>
@@ -11150,7 +11143,7 @@
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B590" s="3" t="s">
         <v>1327</v>
@@ -11158,7 +11151,7 @@
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B591" s="3" t="s">
         <v>1328</v>
@@ -11166,7 +11159,7 @@
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B592" s="3" t="s">
         <v>1329</v>
@@ -11174,7 +11167,7 @@
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593" s="3" t="s">
-        <v>489</v>
+        <v>1727</v>
       </c>
       <c r="B593" s="3" t="s">
         <v>1330</v>
@@ -11182,7 +11175,7 @@
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594" s="3" t="s">
-        <v>1728</v>
+        <v>490</v>
       </c>
       <c r="B594" s="3" t="s">
         <v>1331</v>
@@ -11190,7 +11183,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B595" s="3" t="s">
         <v>1332</v>
@@ -11198,7 +11191,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596" s="3" t="s">
-        <v>491</v>
+        <v>1865</v>
       </c>
       <c r="B596" s="3" t="s">
         <v>1333</v>
@@ -11206,7 +11199,7 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597" s="3" t="s">
-        <v>1866</v>
+        <v>492</v>
       </c>
       <c r="B597" s="3" t="s">
         <v>1334</v>
@@ -11214,7 +11207,7 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B598" s="3" t="s">
         <v>1335</v>
@@ -11222,7 +11215,7 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B599" s="3" t="s">
         <v>1336</v>
@@ -11230,7 +11223,7 @@
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B600" s="3" t="s">
         <v>1337</v>
@@ -11238,7 +11231,7 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B601" s="3" t="s">
         <v>1338</v>
@@ -11246,7 +11239,7 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B602" s="3" t="s">
         <v>1339</v>
@@ -11254,7 +11247,7 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B603" s="3" t="s">
         <v>1340</v>
@@ -11262,7 +11255,7 @@
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B604" s="3" t="s">
         <v>1341</v>
@@ -11270,7 +11263,7 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B605" s="3" t="s">
         <v>1342</v>
@@ -11278,7 +11271,7 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B606" s="3" t="s">
         <v>1343</v>
@@ -11286,7 +11279,7 @@
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607" s="3" t="s">
-        <v>501</v>
+        <v>1728</v>
       </c>
       <c r="B607" s="3" t="s">
         <v>1344</v>
@@ -11294,7 +11287,7 @@
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608" s="3" t="s">
-        <v>1729</v>
+        <v>502</v>
       </c>
       <c r="B608" s="3" t="s">
         <v>1345</v>
@@ -11302,7 +11295,7 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B609" s="3" t="s">
         <v>1346</v>
@@ -11310,7 +11303,7 @@
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B610" s="3" t="s">
         <v>1347</v>
@@ -11318,7 +11311,7 @@
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611" s="3" t="s">
-        <v>504</v>
+        <v>1866</v>
       </c>
       <c r="B611" s="3" t="s">
         <v>1348</v>
@@ -11326,7 +11319,7 @@
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612" s="3" t="s">
-        <v>1867</v>
+        <v>505</v>
       </c>
       <c r="B612" s="3" t="s">
         <v>1349</v>
@@ -11334,7 +11327,7 @@
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A613" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B613" s="3" t="s">
         <v>1350</v>
@@ -11342,7 +11335,7 @@
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A614" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B614" s="3" t="s">
         <v>1351</v>
@@ -11350,7 +11343,7 @@
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A615" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B615" s="3" t="s">
         <v>1352</v>
@@ -11358,7 +11351,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A616" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B616" s="3" t="s">
         <v>1353</v>
@@ -11366,7 +11359,7 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A617" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B617" s="3" t="s">
         <v>1354</v>
@@ -11374,7 +11367,7 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A618" s="3" t="s">
-        <v>510</v>
+        <v>1729</v>
       </c>
       <c r="B618" s="3" t="s">
         <v>1355</v>
@@ -11390,7 +11383,7 @@
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A620" s="3" t="s">
-        <v>1731</v>
+        <v>511</v>
       </c>
       <c r="B620" s="3" t="s">
         <v>1357</v>
@@ -11398,7 +11391,7 @@
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A621" s="3" t="s">
-        <v>511</v>
+        <v>1731</v>
       </c>
       <c r="B621" s="3" t="s">
         <v>1358</v>
@@ -11414,7 +11407,7 @@
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A623" s="3" t="s">
-        <v>1733</v>
+        <v>512</v>
       </c>
       <c r="B623" s="3" t="s">
         <v>1360</v>
@@ -11422,7 +11415,7 @@
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A624" s="3" t="s">
-        <v>512</v>
+        <v>1733</v>
       </c>
       <c r="B624" s="3" t="s">
         <v>1361</v>
@@ -11430,7 +11423,7 @@
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A625" s="3" t="s">
-        <v>1734</v>
+        <v>513</v>
       </c>
       <c r="B625" s="3" t="s">
         <v>1362</v>
@@ -11438,7 +11431,7 @@
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A626" s="3" t="s">
-        <v>513</v>
+        <v>1734</v>
       </c>
       <c r="B626" s="3" t="s">
         <v>1363</v>
@@ -11446,7 +11439,7 @@
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A627" s="3" t="s">
-        <v>1735</v>
+        <v>514</v>
       </c>
       <c r="B627" s="3" t="s">
         <v>1364</v>
@@ -11454,7 +11447,7 @@
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A628" s="3" t="s">
-        <v>514</v>
+        <v>1778</v>
       </c>
       <c r="B628" s="3" t="s">
         <v>1365</v>
@@ -11462,7 +11455,7 @@
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A629" s="3" t="s">
-        <v>1779</v>
+        <v>515</v>
       </c>
       <c r="B629" s="3" t="s">
         <v>1366</v>
@@ -11470,7 +11463,7 @@
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A630" s="3" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B630" s="3" t="s">
         <v>1367</v>
@@ -11478,7 +11471,7 @@
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A631" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B631" s="3" t="s">
         <v>1368</v>
@@ -11486,7 +11479,7 @@
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A632" s="3" t="s">
-        <v>517</v>
+        <v>1735</v>
       </c>
       <c r="B632" s="3" t="s">
         <v>1369</v>
@@ -11494,7 +11487,7 @@
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A633" s="3" t="s">
-        <v>1736</v>
+        <v>714</v>
       </c>
       <c r="B633" s="3" t="s">
         <v>1370</v>
@@ -11502,7 +11495,7 @@
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A634" s="3" t="s">
-        <v>714</v>
+        <v>518</v>
       </c>
       <c r="B634" s="3" t="s">
         <v>1371</v>
@@ -11510,7 +11503,7 @@
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A635" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B635" s="3" t="s">
         <v>1372</v>
@@ -11518,7 +11511,7 @@
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A636" s="3" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B636" s="3" t="s">
         <v>1373</v>
@@ -11526,7 +11519,7 @@
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A637" s="3" t="s">
-        <v>520</v>
+        <v>1779</v>
       </c>
       <c r="B637" s="3" t="s">
         <v>1374</v>
@@ -11534,7 +11527,7 @@
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A638" s="3" t="s">
-        <v>1780</v>
+        <v>521</v>
       </c>
       <c r="B638" s="3" t="s">
         <v>1375</v>
@@ -11542,7 +11535,7 @@
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A639" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B639" s="3" t="s">
         <v>1376</v>
@@ -11550,7 +11543,7 @@
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A640" s="3" t="s">
-        <v>522</v>
+        <v>1736</v>
       </c>
       <c r="B640" s="3" t="s">
         <v>1377</v>
@@ -11558,7 +11551,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A641" s="3" t="s">
-        <v>1737</v>
+        <v>523</v>
       </c>
       <c r="B641" s="3" t="s">
         <v>1378</v>
@@ -11566,7 +11559,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A642" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B642" s="3" t="s">
         <v>1379</v>
@@ -11574,7 +11567,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A643" s="3" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B643" s="3" t="s">
         <v>1380</v>
@@ -11582,7 +11575,7 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A644" s="3" t="s">
-        <v>525</v>
+        <v>1737</v>
       </c>
       <c r="B644" s="3" t="s">
         <v>1381</v>
@@ -11590,7 +11583,7 @@
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A645" s="3" t="s">
-        <v>1738</v>
+        <v>526</v>
       </c>
       <c r="B645" s="3" t="s">
         <v>1382</v>
@@ -11598,7 +11591,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A646" s="3" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B646" s="3" t="s">
         <v>1383</v>
@@ -11606,7 +11599,7 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A647" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B647" s="3" t="s">
         <v>1384</v>
@@ -11614,7 +11607,7 @@
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A648" s="3" t="s">
-        <v>528</v>
+        <v>1738</v>
       </c>
       <c r="B648" s="3" t="s">
         <v>1385</v>
@@ -11622,7 +11615,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A649" s="3" t="s">
-        <v>1739</v>
+        <v>529</v>
       </c>
       <c r="B649" s="3" t="s">
         <v>1386</v>
@@ -11630,7 +11623,7 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A650" s="3" t="s">
-        <v>529</v>
+        <v>1739</v>
       </c>
       <c r="B650" s="3" t="s">
         <v>1387</v>
@@ -11638,7 +11631,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A651" s="3" t="s">
-        <v>1740</v>
+        <v>530</v>
       </c>
       <c r="B651" s="3" t="s">
         <v>1388</v>
@@ -11646,7 +11639,7 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A652" s="3" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B652" s="3" t="s">
         <v>1389</v>
@@ -11654,7 +11647,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A653" s="3" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B653" s="3" t="s">
         <v>1390</v>
@@ -11662,7 +11655,7 @@
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A654" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>1391</v>
@@ -11670,7 +11663,7 @@
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A655" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B655" s="3" t="s">
         <v>1392</v>
@@ -11678,7 +11671,7 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A656" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B656" s="3" t="s">
         <v>1393</v>
@@ -11686,7 +11679,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A657" s="3" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B657" s="3" t="s">
         <v>1394</v>
@@ -11694,7 +11687,7 @@
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A658" s="3" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B658" s="3" t="s">
         <v>1395</v>
@@ -11702,7 +11695,7 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A659" s="3" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B659" s="3" t="s">
         <v>1396</v>
@@ -11710,7 +11703,7 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A660" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B660" s="3" t="s">
         <v>1397</v>
@@ -11718,7 +11711,7 @@
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A661" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B661" s="3" t="s">
         <v>1398</v>
@@ -11726,7 +11719,7 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A662" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B662" s="3" t="s">
         <v>1399</v>
@@ -11734,7 +11727,7 @@
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A663" s="3" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B663" s="3" t="s">
         <v>1400</v>
@@ -11742,7 +11735,7 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A664" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B664" s="3" t="s">
         <v>1401</v>
@@ -11750,7 +11743,7 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A665" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B665" s="3" t="s">
         <v>1402</v>
@@ -11758,7 +11751,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A666" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B666" s="3" t="s">
         <v>1403</v>
@@ -11766,7 +11759,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A667" s="3" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B667" s="3" t="s">
         <v>1404</v>
@@ -11774,7 +11767,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A668" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B668" s="3" t="s">
         <v>1405</v>
@@ -11782,7 +11775,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A669" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B669" s="3" t="s">
         <v>1406</v>
@@ -11790,7 +11783,7 @@
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A670" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B670" s="3" t="s">
         <v>1407</v>
@@ -11798,7 +11791,7 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A671" s="3" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B671" s="3" t="s">
         <v>1408</v>
@@ -11806,7 +11799,7 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A672" s="3" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B672" s="3" t="s">
         <v>1409</v>
@@ -11814,7 +11807,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A673" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B673" s="3" t="s">
         <v>1410</v>
@@ -11822,7 +11815,7 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A674" s="3" t="s">
-        <v>552</v>
+        <v>1926</v>
       </c>
       <c r="B674" s="3" t="s">
         <v>1411</v>
@@ -11830,7 +11823,7 @@
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A675" s="3" t="s">
-        <v>1927</v>
+        <v>553</v>
       </c>
       <c r="B675" s="3" t="s">
         <v>1412</v>
@@ -11838,7 +11831,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A676" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B676" s="3" t="s">
         <v>1413</v>
@@ -11846,7 +11839,7 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A677" s="3" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B677" s="3" t="s">
         <v>1414</v>
@@ -11854,7 +11847,7 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A678" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B678" s="3" t="s">
         <v>1415</v>
@@ -11862,7 +11855,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A679" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B679" s="3" t="s">
         <v>1416</v>
@@ -11870,7 +11863,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A680" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B680" s="3" t="s">
         <v>1417</v>
@@ -11878,7 +11871,7 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A681" s="3" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B681" s="3" t="s">
         <v>1418</v>
@@ -11886,7 +11879,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A682" s="3" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B682" s="3" t="s">
         <v>1419</v>
@@ -11894,7 +11887,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A683" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B683" s="3" t="s">
         <v>1420</v>
@@ -11902,7 +11895,7 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A684" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B684" s="3" t="s">
         <v>1421</v>
@@ -11910,7 +11903,7 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A685" s="3" t="s">
-        <v>562</v>
+        <v>1740</v>
       </c>
       <c r="B685" s="3" t="s">
         <v>1422</v>
@@ -11918,7 +11911,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A686" s="3" t="s">
-        <v>1741</v>
+        <v>563</v>
       </c>
       <c r="B686" s="3" t="s">
         <v>1423</v>
@@ -11926,7 +11919,7 @@
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A687" s="3" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B687" s="3" t="s">
         <v>1424</v>
@@ -11934,7 +11927,7 @@
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A688" s="3" t="s">
-        <v>564</v>
+        <v>1867</v>
       </c>
       <c r="B688" s="3" t="s">
         <v>1425</v>
@@ -11942,7 +11935,7 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A689" s="3" t="s">
-        <v>1868</v>
+        <v>565</v>
       </c>
       <c r="B689" s="3" t="s">
         <v>1426</v>
@@ -11950,7 +11943,7 @@
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A690" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B690" s="3" t="s">
         <v>1427</v>
@@ -11958,7 +11951,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A691" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B691" s="3" t="s">
         <v>1428</v>
@@ -11966,7 +11959,7 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A692" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B692" s="3" t="s">
         <v>1429</v>
@@ -11974,7 +11967,7 @@
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A693" s="3" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B693" s="3" t="s">
         <v>1430</v>
@@ -11982,7 +11975,7 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A694" s="3" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B694" s="3" t="s">
         <v>1431</v>
@@ -11990,7 +11983,7 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A695" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B695" s="3" t="s">
         <v>1432</v>
@@ -11998,7 +11991,7 @@
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A696" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B696" s="3" t="s">
         <v>1433</v>
@@ -12006,7 +11999,7 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A697" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B697" s="3" t="s">
         <v>1434</v>
@@ -12014,7 +12007,7 @@
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A698" s="3" t="s">
-        <v>573</v>
+        <v>1868</v>
       </c>
       <c r="B698" s="3" t="s">
         <v>1435</v>
@@ -12022,7 +12015,7 @@
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A699" s="3" t="s">
-        <v>1869</v>
+        <v>574</v>
       </c>
       <c r="B699" s="3" t="s">
         <v>1436</v>
@@ -12030,7 +12023,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A700" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B700" s="3" t="s">
         <v>1437</v>
@@ -12038,7 +12031,7 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A701" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B701" s="3" t="s">
         <v>1438</v>
@@ -12046,7 +12039,7 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A702" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B702" s="3" t="s">
         <v>1439</v>
@@ -12054,7 +12047,7 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A703" s="3" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B703" s="3" t="s">
         <v>1440</v>
@@ -12062,7 +12055,7 @@
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A704" s="3" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B704" s="3" t="s">
         <v>1441</v>
@@ -12070,7 +12063,7 @@
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A705" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B705" s="3" t="s">
         <v>1442</v>
@@ -12078,7 +12071,7 @@
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A706" s="3" t="s">
-        <v>580</v>
+        <v>1741</v>
       </c>
       <c r="B706" s="3" t="s">
         <v>1443</v>
@@ -12086,7 +12079,7 @@
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A707" s="3" t="s">
-        <v>1742</v>
+        <v>1869</v>
       </c>
       <c r="B707" s="3" t="s">
         <v>1444</v>
@@ -12102,7 +12095,7 @@
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A709" s="3" t="s">
-        <v>1871</v>
+        <v>581</v>
       </c>
       <c r="B709" s="3" t="s">
         <v>1446</v>
@@ -12110,7 +12103,7 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A710" s="3" t="s">
-        <v>581</v>
+        <v>1871</v>
       </c>
       <c r="B710" s="3" t="s">
         <v>1447</v>
@@ -12126,7 +12119,7 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A712" s="3" t="s">
-        <v>1873</v>
+        <v>582</v>
       </c>
       <c r="B712" s="3" t="s">
         <v>1449</v>
@@ -12134,7 +12127,7 @@
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A713" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B713" s="3" t="s">
         <v>1450</v>
@@ -12142,7 +12135,7 @@
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A714" s="3" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B714" s="3" t="s">
         <v>1451</v>
@@ -12150,7 +12143,7 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A715" s="3" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B715" s="3" t="s">
         <v>1452</v>
@@ -12158,7 +12151,7 @@
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A716" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B716" s="3" t="s">
         <v>1453</v>
@@ -12166,7 +12159,7 @@
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A717" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B717" s="3" t="s">
         <v>1454</v>
@@ -12174,7 +12167,7 @@
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A718" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B718" s="3" t="s">
         <v>1455</v>
@@ -12182,7 +12175,7 @@
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A719" s="3" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B719" s="3" t="s">
         <v>1456</v>
@@ -12190,7 +12183,7 @@
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A720" s="3" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B720" s="3" t="s">
         <v>1457</v>
@@ -12198,7 +12191,7 @@
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A721" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B721" s="3" t="s">
         <v>1458</v>
@@ -12206,7 +12199,7 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A722" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B722" s="3" t="s">
         <v>1459</v>
@@ -12214,7 +12207,7 @@
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A723" s="3" t="s">
-        <v>592</v>
+        <v>1873</v>
       </c>
       <c r="B723" s="3" t="s">
         <v>1460</v>
@@ -12222,7 +12215,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A724" s="3" t="s">
-        <v>1874</v>
+        <v>593</v>
       </c>
       <c r="B724" s="3" t="s">
         <v>1461</v>
@@ -12230,7 +12223,7 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A725" s="3" t="s">
-        <v>593</v>
+        <v>1874</v>
       </c>
       <c r="B725" s="3" t="s">
         <v>1462</v>
@@ -12238,7 +12231,7 @@
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A726" s="3" t="s">
-        <v>1875</v>
+        <v>594</v>
       </c>
       <c r="B726" s="3" t="s">
         <v>1463</v>
@@ -12246,7 +12239,7 @@
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A727" s="3" t="s">
-        <v>594</v>
+        <v>1933</v>
       </c>
       <c r="B727" s="3" t="s">
         <v>1464</v>
@@ -12254,7 +12247,7 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A728" s="3" t="s">
-        <v>1935</v>
+        <v>595</v>
       </c>
       <c r="B728" s="3" t="s">
         <v>1465</v>
@@ -12262,7 +12255,7 @@
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A729" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B729" s="3" t="s">
         <v>1466</v>
@@ -12270,7 +12263,7 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A730" s="3" t="s">
-        <v>596</v>
+        <v>1875</v>
       </c>
       <c r="B730" s="3" t="s">
         <v>1467</v>
@@ -12278,7 +12271,7 @@
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A731" s="3" t="s">
-        <v>1876</v>
+        <v>597</v>
       </c>
       <c r="B731" s="3" t="s">
         <v>1468</v>
@@ -12286,7 +12279,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A732" s="3" t="s">
-        <v>597</v>
+        <v>1876</v>
       </c>
       <c r="B732" s="3" t="s">
         <v>1469</v>
@@ -12294,7 +12287,7 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A733" s="3" t="s">
-        <v>1877</v>
+        <v>598</v>
       </c>
       <c r="B733" s="3" t="s">
         <v>1470</v>
@@ -12302,7 +12295,7 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A734" s="3" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B734" s="3" t="s">
         <v>1471</v>
@@ -12310,7 +12303,7 @@
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A735" s="3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B735" s="3" t="s">
         <v>1472</v>
@@ -12318,7 +12311,7 @@
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A736" s="3" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B736" s="3" t="s">
         <v>1473</v>
@@ -12326,7 +12319,7 @@
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A737" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B737" s="3" t="s">
         <v>1474</v>
@@ -12334,7 +12327,7 @@
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A738" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B738" s="3" t="s">
         <v>1475</v>
@@ -12342,7 +12335,7 @@
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A739" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B739" s="3" t="s">
         <v>1476</v>
@@ -12350,7 +12343,7 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A740" s="3" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B740" s="3" t="s">
         <v>1477</v>
@@ -12358,7 +12351,7 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A741" s="3" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B741" s="3" t="s">
         <v>1478</v>
@@ -12366,7 +12359,7 @@
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A742" s="3" t="s">
-        <v>606</v>
+        <v>1877</v>
       </c>
       <c r="B742" s="3" t="s">
         <v>1479</v>
@@ -12374,7 +12367,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A743" s="3" t="s">
-        <v>1878</v>
+        <v>607</v>
       </c>
       <c r="B743" s="3" t="s">
         <v>1480</v>
@@ -12382,7 +12375,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A744" s="3" t="s">
-        <v>607</v>
+        <v>1878</v>
       </c>
       <c r="B744" s="3" t="s">
         <v>1481</v>
@@ -12398,7 +12391,7 @@
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A746" s="3" t="s">
-        <v>1880</v>
+        <v>1927</v>
       </c>
       <c r="B746" s="3" t="s">
         <v>1483</v>
@@ -12406,7 +12399,7 @@
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A747" s="3" t="s">
-        <v>1928</v>
+        <v>608</v>
       </c>
       <c r="B747" s="3" t="s">
         <v>1484</v>
@@ -12414,7 +12407,7 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A748" s="3" t="s">
-        <v>608</v>
+        <v>1742</v>
       </c>
       <c r="B748" s="3" t="s">
         <v>1485</v>
@@ -12422,7 +12415,7 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A749" s="3" t="s">
-        <v>1743</v>
+        <v>1880</v>
       </c>
       <c r="B749" s="3" t="s">
         <v>1486</v>
@@ -12446,7 +12439,7 @@
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A752" s="3" t="s">
-        <v>1883</v>
+        <v>609</v>
       </c>
       <c r="B752" s="3" t="s">
         <v>1489</v>
@@ -12454,7 +12447,7 @@
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A753" s="3" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B753" s="3" t="s">
         <v>1490</v>
@@ -12462,7 +12455,7 @@
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A754" s="3" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B754" s="3" t="s">
         <v>1491</v>
@@ -12470,7 +12463,7 @@
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A755" s="3" t="s">
-        <v>611</v>
+        <v>1928</v>
       </c>
       <c r="B755" s="3" t="s">
         <v>1492</v>
@@ -12486,7 +12479,7 @@
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A757" s="3" t="s">
-        <v>1930</v>
+        <v>612</v>
       </c>
       <c r="B757" s="3" t="s">
         <v>1494</v>
@@ -12494,7 +12487,7 @@
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A758" s="3" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B758" s="3" t="s">
         <v>1495</v>
@@ -12502,7 +12495,7 @@
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A759" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B759" s="3" t="s">
         <v>1496</v>
@@ -12510,7 +12503,7 @@
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A760" s="3" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B760" s="3" t="s">
         <v>1497</v>
@@ -12518,7 +12511,7 @@
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A761" s="3" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B761" s="3" t="s">
         <v>1498</v>
@@ -12526,7 +12519,7 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A762" s="3" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B762" s="3" t="s">
         <v>1499</v>
@@ -12534,7 +12527,7 @@
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A763" s="3" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B763" s="3" t="s">
         <v>1500</v>
@@ -12542,7 +12535,7 @@
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A764" s="3" t="s">
-        <v>618</v>
+        <v>1883</v>
       </c>
       <c r="B764" s="3" t="s">
         <v>1501</v>
@@ -12550,7 +12543,7 @@
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A765" s="3" t="s">
-        <v>1884</v>
+        <v>619</v>
       </c>
       <c r="B765" s="3" t="s">
         <v>1502</v>
@@ -12558,7 +12551,7 @@
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A766" s="3" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B766" s="3" t="s">
         <v>1503</v>
@@ -12566,7 +12559,7 @@
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A767" s="3" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B767" s="3" t="s">
         <v>1504</v>
@@ -12574,7 +12567,7 @@
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A768" s="3" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B768" s="3" t="s">
         <v>1505</v>
@@ -12582,7 +12575,7 @@
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A769" s="3" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B769" s="3" t="s">
         <v>1506</v>
@@ -12590,7 +12583,7 @@
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A770" s="3" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B770" s="3" t="s">
         <v>1507</v>
@@ -12598,7 +12591,7 @@
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A771" s="3" t="s">
-        <v>624</v>
+        <v>1664</v>
       </c>
       <c r="B771" s="3" t="s">
         <v>1508</v>
@@ -12606,7 +12599,7 @@
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A772" s="3" t="s">
-        <v>1665</v>
+        <v>1934</v>
       </c>
       <c r="B772" s="3" t="s">
         <v>1509</v>
@@ -12614,7 +12607,7 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A773" s="3" t="s">
-        <v>1936</v>
+        <v>625</v>
       </c>
       <c r="B773" s="3" t="s">
         <v>1510</v>
@@ -12622,7 +12615,7 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A774" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B774" s="3" t="s">
         <v>1511</v>
@@ -12630,7 +12623,7 @@
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A775" s="3" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B775" s="3" t="s">
         <v>1512</v>
@@ -12638,7 +12631,7 @@
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A776" s="3" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B776" s="3" t="s">
         <v>1513</v>
@@ -12646,7 +12639,7 @@
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A777" s="3" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B777" s="3" t="s">
         <v>1514</v>
@@ -12654,15 +12647,15 @@
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A778" s="3" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B778" s="3" t="s">
         <v>1515</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A779" s="3" t="s">
-        <v>630</v>
+      <c r="A779" s="4" t="s">
+        <v>1743</v>
       </c>
       <c r="B779" s="3" t="s">
         <v>1516</v>
@@ -12678,7 +12671,7 @@
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A781" s="4" t="s">
-        <v>1745</v>
+        <v>1884</v>
       </c>
       <c r="B781" s="3" t="s">
         <v>1518</v>
@@ -12686,10 +12679,10 @@
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A782" s="4" t="s">
-        <v>1885</v>
+        <v>1745</v>
       </c>
       <c r="B782" s="3" t="s">
-        <v>1519</v>
+        <v>728</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.3">
@@ -12697,12 +12690,12 @@
         <v>1746</v>
       </c>
       <c r="B783" s="3" t="s">
-        <v>728</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A784" s="4" t="s">
-        <v>1747</v>
+        <v>631</v>
       </c>
       <c r="B784" s="3" t="s">
         <v>1520</v>
@@ -12710,23 +12703,23 @@
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A785" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B785" s="3" t="s">
-        <v>1521</v>
+        <v>731</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A786" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B786" s="3" t="s">
-        <v>731</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A787" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B787" s="3" t="s">
         <v>1522</v>
@@ -12734,7 +12727,7 @@
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A788" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B788" s="3" t="s">
         <v>1523</v>
@@ -12742,7 +12735,7 @@
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A789" s="4" t="s">
-        <v>635</v>
+        <v>1885</v>
       </c>
       <c r="B789" s="3" t="s">
         <v>1524</v>
@@ -12750,7 +12743,7 @@
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A790" s="4" t="s">
-        <v>1886</v>
+        <v>1772</v>
       </c>
       <c r="B790" s="3" t="s">
         <v>1525</v>
@@ -12758,23 +12751,23 @@
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A791" s="4" t="s">
-        <v>1773</v>
+        <v>636</v>
       </c>
       <c r="B791" s="3" t="s">
-        <v>1526</v>
+        <v>729</v>
       </c>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A792" s="4" t="s">
-        <v>636</v>
+        <v>1886</v>
       </c>
       <c r="B792" s="3" t="s">
-        <v>729</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A793" s="4" t="s">
-        <v>1887</v>
+        <v>637</v>
       </c>
       <c r="B793" s="3" t="s">
         <v>1527</v>
@@ -12782,7 +12775,7 @@
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A794" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B794" s="3" t="s">
         <v>1528</v>
@@ -12790,7 +12783,7 @@
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A795" s="4" t="s">
-        <v>638</v>
+        <v>1887</v>
       </c>
       <c r="B795" s="3" t="s">
         <v>1529</v>
@@ -12798,7 +12791,7 @@
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A796" s="4" t="s">
-        <v>1888</v>
+        <v>639</v>
       </c>
       <c r="B796" s="3" t="s">
         <v>1530</v>
@@ -12806,7 +12799,7 @@
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A797" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B797" s="3" t="s">
         <v>1531</v>
@@ -12814,7 +12807,7 @@
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A798" s="4" t="s">
-        <v>640</v>
+        <v>1888</v>
       </c>
       <c r="B798" s="3" t="s">
         <v>1532</v>
@@ -12822,7 +12815,7 @@
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A799" s="4" t="s">
-        <v>1889</v>
+        <v>641</v>
       </c>
       <c r="B799" s="3" t="s">
         <v>1533</v>
@@ -12830,7 +12823,7 @@
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A800" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B800" s="3" t="s">
         <v>1534</v>
@@ -12838,7 +12831,7 @@
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A801" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B801" s="3" t="s">
         <v>1535</v>
@@ -12846,7 +12839,7 @@
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A802" s="4" t="s">
-        <v>643</v>
+        <v>1773</v>
       </c>
       <c r="B802" s="3" t="s">
         <v>1536</v>
@@ -12854,7 +12847,7 @@
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A803" s="4" t="s">
-        <v>1774</v>
+        <v>644</v>
       </c>
       <c r="B803" s="3" t="s">
         <v>1537</v>
@@ -12862,7 +12855,7 @@
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A804" s="4" t="s">
-        <v>644</v>
+        <v>1889</v>
       </c>
       <c r="B804" s="3" t="s">
         <v>1538</v>
@@ -12870,7 +12863,7 @@
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A805" s="4" t="s">
-        <v>1890</v>
+        <v>645</v>
       </c>
       <c r="B805" s="3" t="s">
         <v>1539</v>
@@ -12878,7 +12871,7 @@
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A806" s="4" t="s">
-        <v>645</v>
+        <v>1774</v>
       </c>
       <c r="B806" s="3" t="s">
         <v>1540</v>
@@ -12886,7 +12879,7 @@
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A807" s="4" t="s">
-        <v>1775</v>
+        <v>1890</v>
       </c>
       <c r="B807" s="3" t="s">
         <v>1541</v>
@@ -12894,7 +12887,7 @@
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A808" s="4" t="s">
-        <v>1891</v>
+        <v>646</v>
       </c>
       <c r="B808" s="3" t="s">
         <v>1542</v>
@@ -12902,7 +12895,7 @@
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A809" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B809" s="3" t="s">
         <v>1543</v>
@@ -12910,7 +12903,7 @@
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A810" s="4" t="s">
-        <v>647</v>
+        <v>1891</v>
       </c>
       <c r="B810" s="3" t="s">
         <v>1544</v>
@@ -12918,7 +12911,7 @@
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A811" s="4" t="s">
-        <v>1892</v>
+        <v>648</v>
       </c>
       <c r="B811" s="3" t="s">
         <v>1545</v>
@@ -12926,7 +12919,7 @@
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A812" s="4" t="s">
-        <v>648</v>
+        <v>1747</v>
       </c>
       <c r="B812" s="3" t="s">
         <v>1546</v>
@@ -12934,7 +12927,7 @@
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A813" s="4" t="s">
-        <v>1748</v>
+        <v>1892</v>
       </c>
       <c r="B813" s="3" t="s">
         <v>1547</v>
@@ -12942,7 +12935,7 @@
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A814" s="4" t="s">
-        <v>1893</v>
+        <v>1748</v>
       </c>
       <c r="B814" s="3" t="s">
         <v>1548</v>
@@ -12966,7 +12959,7 @@
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A817" s="4" t="s">
-        <v>1751</v>
+        <v>1893</v>
       </c>
       <c r="B817" s="3" t="s">
         <v>1551</v>
@@ -12974,7 +12967,7 @@
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A818" s="4" t="s">
-        <v>1894</v>
+        <v>1751</v>
       </c>
       <c r="B818" s="3" t="s">
         <v>1552</v>
@@ -12982,7 +12975,7 @@
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A819" s="4" t="s">
-        <v>1752</v>
+        <v>649</v>
       </c>
       <c r="B819" s="3" t="s">
         <v>1553</v>
@@ -12990,7 +12983,7 @@
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A820" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B820" s="3" t="s">
         <v>1554</v>
@@ -12998,7 +12991,7 @@
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A821" s="4" t="s">
-        <v>650</v>
+        <v>1894</v>
       </c>
       <c r="B821" s="3" t="s">
         <v>1555</v>
@@ -13006,7 +12999,7 @@
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A822" s="4" t="s">
-        <v>1895</v>
+        <v>651</v>
       </c>
       <c r="B822" s="3" t="s">
         <v>1556</v>
@@ -13014,7 +13007,7 @@
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A823" s="4" t="s">
-        <v>651</v>
+        <v>1895</v>
       </c>
       <c r="B823" s="3" t="s">
         <v>1557</v>
@@ -13022,7 +13015,7 @@
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A824" s="4" t="s">
-        <v>1896</v>
+        <v>1752</v>
       </c>
       <c r="B824" s="3" t="s">
         <v>1558</v>
@@ -13030,7 +13023,7 @@
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A825" s="4" t="s">
-        <v>1753</v>
+        <v>652</v>
       </c>
       <c r="B825" s="3" t="s">
         <v>1559</v>
@@ -13038,7 +13031,7 @@
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A826" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B826" s="3" t="s">
         <v>1560</v>
@@ -13046,7 +13039,7 @@
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A827" s="4" t="s">
-        <v>653</v>
+        <v>1753</v>
       </c>
       <c r="B827" s="3" t="s">
         <v>1561</v>
@@ -13062,7 +13055,7 @@
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A829" s="4" t="s">
-        <v>1755</v>
+        <v>1896</v>
       </c>
       <c r="B829" s="3" t="s">
         <v>1563</v>
@@ -13102,7 +13095,7 @@
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A834" s="4" t="s">
-        <v>1901</v>
+        <v>654</v>
       </c>
       <c r="B834" s="3" t="s">
         <v>1568</v>
@@ -13110,7 +13103,7 @@
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A835" s="4" t="s">
-        <v>654</v>
+        <v>1755</v>
       </c>
       <c r="B835" s="3" t="s">
         <v>1569</v>
@@ -13126,7 +13119,7 @@
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A837" s="4" t="s">
-        <v>1757</v>
+        <v>1901</v>
       </c>
       <c r="B837" s="3" t="s">
         <v>1571</v>
@@ -13134,7 +13127,7 @@
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A838" s="4" t="s">
-        <v>1902</v>
+        <v>655</v>
       </c>
       <c r="B838" s="3" t="s">
         <v>1572</v>
@@ -13142,7 +13135,7 @@
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A839" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B839" s="3" t="s">
         <v>1573</v>
@@ -13150,7 +13143,7 @@
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A840" s="4" t="s">
-        <v>656</v>
+        <v>1757</v>
       </c>
       <c r="B840" s="3" t="s">
         <v>1574</v>
@@ -13158,7 +13151,7 @@
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A841" s="4" t="s">
-        <v>1758</v>
+        <v>1902</v>
       </c>
       <c r="B841" s="3" t="s">
         <v>1575</v>
@@ -13166,7 +13159,7 @@
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A842" s="4" t="s">
-        <v>1903</v>
+        <v>1780</v>
       </c>
       <c r="B842" s="3" t="s">
         <v>1576</v>
@@ -13182,167 +13175,167 @@
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A844" s="4" t="s">
-        <v>1782</v>
+        <v>1903</v>
       </c>
       <c r="B844" s="3" t="s">
         <v>1578</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A845" s="4" t="s">
-        <v>1904</v>
+      <c r="A845" s="2" t="s">
+        <v>657</v>
       </c>
       <c r="B845" s="3" t="s">
-        <v>1579</v>
+        <v>658</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A846" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="B846" s="3" t="s">
-        <v>658</v>
+        <v>659</v>
+      </c>
+      <c r="B846" s="9" t="s">
+        <v>1579</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A847" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B847" s="9" t="s">
-        <v>1580</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A848" s="2" t="s">
-        <v>660</v>
+      <c r="A848" s="7" t="s">
+        <v>1758</v>
       </c>
       <c r="B848" s="9" t="s">
-        <v>1505</v>
+        <v>667</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A849" s="7" t="s">
-        <v>1759</v>
+      <c r="A849" s="8" t="s">
+        <v>662</v>
       </c>
       <c r="B849" s="9" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A850" s="8" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B850" s="9" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A851" s="8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B851" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A852" s="8" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B852" s="9" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A853" s="8" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B853" s="9" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A854" s="8" t="s">
-        <v>666</v>
+        <v>1759</v>
       </c>
       <c r="B854" s="9" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A855" s="8" t="s">
-        <v>1760</v>
+        <v>1904</v>
       </c>
       <c r="B855" s="9" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A856" s="8" t="s">
+      <c r="A856" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B856" s="9" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="857" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A857" s="8" t="s">
         <v>1905</v>
       </c>
-      <c r="B856" s="9" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="857" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A857" s="6" t="s">
-        <v>661</v>
-      </c>
       <c r="B857" s="9" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A858" s="8" t="s">
-        <v>1906</v>
+        <v>681</v>
       </c>
       <c r="B858" s="9" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A859" s="8" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B859" s="9" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A860" s="8" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B860" s="9" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A861" s="8" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B861" s="9" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A862" s="8" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="B862" s="9" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A863" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="B863" s="9" t="s">
-        <v>686</v>
+      <c r="A863" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B863" s="3" t="s">
+        <v>1580</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A864" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B864" s="3" t="s">
         <v>1581</v>
@@ -13350,7 +13343,7 @@
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A865" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B865" s="3" t="s">
         <v>1582</v>
@@ -13358,7 +13351,7 @@
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A866" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B866" s="3" t="s">
         <v>1583</v>
@@ -13366,7 +13359,7 @@
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A867" s="3" t="s">
-        <v>203</v>
+        <v>1906</v>
       </c>
       <c r="B867" s="3" t="s">
         <v>1584</v>
@@ -13374,7 +13367,7 @@
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A868" s="3" t="s">
-        <v>1907</v>
+        <v>204</v>
       </c>
       <c r="B868" s="3" t="s">
         <v>1585</v>
@@ -13382,7 +13375,7 @@
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A869" s="3" t="s">
-        <v>204</v>
+        <v>1760</v>
       </c>
       <c r="B869" s="3" t="s">
         <v>1586</v>
@@ -13390,7 +13383,7 @@
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A870" s="3" t="s">
-        <v>1761</v>
+        <v>205</v>
       </c>
       <c r="B870" s="3" t="s">
         <v>1587</v>
@@ -13398,7 +13391,7 @@
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A871" s="3" t="s">
-        <v>205</v>
+        <v>1907</v>
       </c>
       <c r="B871" s="3" t="s">
         <v>1588</v>
@@ -13406,7 +13399,7 @@
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A872" s="3" t="s">
-        <v>1908</v>
+        <v>206</v>
       </c>
       <c r="B872" s="3" t="s">
         <v>1589</v>
@@ -13414,7 +13407,7 @@
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A873" s="3" t="s">
-        <v>206</v>
+        <v>1908</v>
       </c>
       <c r="B873" s="3" t="s">
         <v>1590</v>
@@ -13422,7 +13415,7 @@
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A874" s="3" t="s">
-        <v>1909</v>
+        <v>207</v>
       </c>
       <c r="B874" s="3" t="s">
         <v>1591</v>
@@ -13430,7 +13423,7 @@
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A875" s="3" t="s">
-        <v>207</v>
+        <v>1909</v>
       </c>
       <c r="B875" s="3" t="s">
         <v>1592</v>
@@ -13438,7 +13431,7 @@
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A876" s="3" t="s">
-        <v>1910</v>
+        <v>208</v>
       </c>
       <c r="B876" s="3" t="s">
         <v>1593</v>
@@ -13446,7 +13439,7 @@
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A877" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B877" s="3" t="s">
         <v>1594</v>
@@ -13454,7 +13447,7 @@
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A878" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B878" s="3" t="s">
         <v>1595</v>
@@ -13462,7 +13455,7 @@
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A879" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B879" s="3" t="s">
         <v>1596</v>
@@ -13470,7 +13463,7 @@
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A880" s="3" t="s">
-        <v>211</v>
+        <v>1910</v>
       </c>
       <c r="B880" s="3" t="s">
         <v>1597</v>
@@ -13478,7 +13471,7 @@
     </row>
     <row r="881" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A881" s="3" t="s">
-        <v>1911</v>
+        <v>212</v>
       </c>
       <c r="B881" s="3" t="s">
         <v>1598</v>
@@ -13486,7 +13479,7 @@
     </row>
     <row r="882" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A882" s="3" t="s">
-        <v>212</v>
+        <v>1911</v>
       </c>
       <c r="B882" s="3" t="s">
         <v>1599</v>
@@ -13494,7 +13487,7 @@
     </row>
     <row r="883" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A883" s="3" t="s">
-        <v>1912</v>
+        <v>213</v>
       </c>
       <c r="B883" s="3" t="s">
         <v>1600</v>
@@ -13502,7 +13495,7 @@
     </row>
     <row r="884" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A884" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B884" s="3" t="s">
         <v>1601</v>
@@ -13510,7 +13503,7 @@
     </row>
     <row r="885" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A885" s="3" t="s">
-        <v>214</v>
+        <v>1761</v>
       </c>
       <c r="B885" s="3" t="s">
         <v>1602</v>
@@ -13518,7 +13511,7 @@
     </row>
     <row r="886" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A886" s="3" t="s">
-        <v>1762</v>
+        <v>1912</v>
       </c>
       <c r="B886" s="3" t="s">
         <v>1603</v>
@@ -13526,7 +13519,7 @@
     </row>
     <row r="887" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A887" s="3" t="s">
-        <v>1913</v>
+        <v>215</v>
       </c>
       <c r="B887" s="3" t="s">
         <v>1604</v>
@@ -13534,7 +13527,7 @@
     </row>
     <row r="888" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A888" s="3" t="s">
-        <v>215</v>
+        <v>1913</v>
       </c>
       <c r="B888" s="3" t="s">
         <v>1605</v>
@@ -13542,7 +13535,7 @@
     </row>
     <row r="889" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A889" s="3" t="s">
-        <v>1914</v>
+        <v>216</v>
       </c>
       <c r="B889" s="3" t="s">
         <v>1606</v>
@@ -13550,7 +13543,7 @@
     </row>
     <row r="890" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A890" s="3" t="s">
-        <v>216</v>
+        <v>1914</v>
       </c>
       <c r="B890" s="3" t="s">
         <v>1607</v>
@@ -13574,7 +13567,7 @@
     </row>
     <row r="893" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A893" s="3" t="s">
-        <v>1917</v>
+        <v>217</v>
       </c>
       <c r="B893" s="3" t="s">
         <v>1610</v>
@@ -13582,7 +13575,7 @@
     </row>
     <row r="894" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A894" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B894" s="3" t="s">
         <v>1611</v>
@@ -13590,7 +13583,7 @@
     </row>
     <row r="895" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A895" s="3" t="s">
-        <v>218</v>
+        <v>1762</v>
       </c>
       <c r="B895" s="3" t="s">
         <v>1612</v>
@@ -13598,7 +13591,7 @@
     </row>
     <row r="896" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A896" s="3" t="s">
-        <v>1763</v>
+        <v>219</v>
       </c>
       <c r="B896" s="3" t="s">
         <v>1613</v>
@@ -13606,7 +13599,7 @@
     </row>
     <row r="897" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A897" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B897" s="3" t="s">
         <v>1614</v>
@@ -13614,7 +13607,7 @@
     </row>
     <row r="898" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A898" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B898" s="3" t="s">
         <v>1615</v>
@@ -13622,7 +13615,7 @@
     </row>
     <row r="899" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A899" s="3" t="s">
-        <v>221</v>
+        <v>1917</v>
       </c>
       <c r="B899" s="3" t="s">
         <v>1616</v>
@@ -13630,7 +13623,7 @@
     </row>
     <row r="900" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A900" s="3" t="s">
-        <v>1918</v>
+        <v>222</v>
       </c>
       <c r="B900" s="3" t="s">
         <v>1617</v>
@@ -13638,7 +13631,7 @@
     </row>
     <row r="901" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A901" s="3" t="s">
-        <v>222</v>
+        <v>1763</v>
       </c>
       <c r="B901" s="3" t="s">
         <v>1618</v>
@@ -13646,7 +13639,7 @@
     </row>
     <row r="902" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A902" s="3" t="s">
-        <v>1764</v>
+        <v>1918</v>
       </c>
       <c r="B902" s="3" t="s">
         <v>1619</v>
@@ -13654,7 +13647,7 @@
     </row>
     <row r="903" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A903" s="3" t="s">
-        <v>1919</v>
+        <v>223</v>
       </c>
       <c r="B903" s="3" t="s">
         <v>1620</v>
@@ -13662,7 +13655,7 @@
     </row>
     <row r="904" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A904" s="3" t="s">
-        <v>223</v>
+        <v>1919</v>
       </c>
       <c r="B904" s="3" t="s">
         <v>1621</v>
@@ -13670,7 +13663,7 @@
     </row>
     <row r="905" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A905" s="3" t="s">
-        <v>1920</v>
+        <v>224</v>
       </c>
       <c r="B905" s="3" t="s">
         <v>1622</v>
@@ -13678,7 +13671,7 @@
     </row>
     <row r="906" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A906" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B906" s="3" t="s">
         <v>1623</v>
@@ -13686,7 +13679,7 @@
     </row>
     <row r="907" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A907" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B907" s="3" t="s">
         <v>1624</v>
@@ -13694,7 +13687,7 @@
     </row>
     <row r="908" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A908" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B908" s="3" t="s">
         <v>1625</v>
@@ -13702,7 +13695,7 @@
     </row>
     <row r="909" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A909" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B909" s="3" t="s">
         <v>1626</v>
@@ -13710,7 +13703,7 @@
     </row>
     <row r="910" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A910" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B910" s="3" t="s">
         <v>1627</v>
@@ -13718,7 +13711,7 @@
     </row>
     <row r="911" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A911" s="3" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="B911" s="3" t="s">
         <v>1628</v>
@@ -13726,7 +13719,7 @@
     </row>
     <row r="912" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A912" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B912" s="3" t="s">
         <v>1629</v>
@@ -13734,7 +13727,7 @@
     </row>
     <row r="913" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A913" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B913" s="3" t="s">
         <v>1630</v>
@@ -13742,7 +13735,7 @@
     </row>
     <row r="914" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A914" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B914" s="3" t="s">
         <v>1631</v>
@@ -13750,7 +13743,7 @@
     </row>
     <row r="915" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A915" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B915" s="3" t="s">
         <v>1632</v>
@@ -13758,7 +13751,7 @@
     </row>
     <row r="916" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A916" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B916" s="3" t="s">
         <v>1633</v>
@@ -13766,7 +13759,7 @@
     </row>
     <row r="917" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A917" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B917" s="3" t="s">
         <v>1634</v>
@@ -13774,7 +13767,7 @@
     </row>
     <row r="918" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A918" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B918" s="3" t="s">
         <v>1635</v>
@@ -13782,7 +13775,7 @@
     </row>
     <row r="919" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A919" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B919" s="3" t="s">
         <v>1636</v>
@@ -13790,7 +13783,7 @@
     </row>
     <row r="920" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A920" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B920" s="3" t="s">
         <v>1637</v>
@@ -13798,7 +13791,7 @@
     </row>
     <row r="921" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A921" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B921" s="3" t="s">
         <v>1638</v>
@@ -13806,7 +13799,7 @@
     </row>
     <row r="922" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A922" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B922" s="3" t="s">
         <v>1639</v>
@@ -13814,7 +13807,7 @@
     </row>
     <row r="923" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A923" s="3" t="s">
-        <v>255</v>
+        <v>230</v>
       </c>
       <c r="B923" s="3" t="s">
         <v>1640</v>
@@ -13822,7 +13815,7 @@
     </row>
     <row r="924" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A924" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B924" s="3" t="s">
         <v>1641</v>
@@ -13830,7 +13823,7 @@
     </row>
     <row r="925" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A925" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B925" s="3" t="s">
         <v>1642</v>
@@ -13838,7 +13831,7 @@
     </row>
     <row r="926" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A926" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B926" s="3" t="s">
         <v>1643</v>
@@ -13846,7 +13839,7 @@
     </row>
     <row r="927" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A927" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B927" s="3" t="s">
         <v>1644</v>
@@ -13854,7 +13847,7 @@
     </row>
     <row r="928" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A928" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B928" s="3" t="s">
         <v>1645</v>
@@ -13862,7 +13855,7 @@
     </row>
     <row r="929" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A929" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B929" s="3" t="s">
         <v>1646</v>
@@ -13870,7 +13863,7 @@
     </row>
     <row r="930" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A930" s="3" t="s">
-        <v>236</v>
+        <v>1920</v>
       </c>
       <c r="B930" s="3" t="s">
         <v>1647</v>
@@ -13878,7 +13871,7 @@
     </row>
     <row r="931" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A931" s="3" t="s">
-        <v>1921</v>
+        <v>237</v>
       </c>
       <c r="B931" s="3" t="s">
         <v>1648</v>
@@ -13886,7 +13879,7 @@
     </row>
     <row r="932" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A932" s="3" t="s">
-        <v>237</v>
+        <v>1921</v>
       </c>
       <c r="B932" s="3" t="s">
         <v>1649</v>
@@ -13894,7 +13887,7 @@
     </row>
     <row r="933" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A933" s="3" t="s">
-        <v>1922</v>
+        <v>238</v>
       </c>
       <c r="B933" s="3" t="s">
         <v>1650</v>
@@ -13902,7 +13895,7 @@
     </row>
     <row r="934" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A934" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B934" s="3" t="s">
         <v>1651</v>
@@ -13910,7 +13903,7 @@
     </row>
     <row r="935" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A935" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B935" s="3" t="s">
         <v>1652</v>
@@ -13918,7 +13911,7 @@
     </row>
     <row r="936" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A936" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B936" s="3" t="s">
         <v>1653</v>
@@ -13926,7 +13919,7 @@
     </row>
     <row r="937" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A937" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B937" s="3" t="s">
         <v>1654</v>
@@ -13934,7 +13927,7 @@
     </row>
     <row r="938" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A938" s="3" t="s">
-        <v>242</v>
+        <v>1922</v>
       </c>
       <c r="B938" s="3" t="s">
         <v>1655</v>
@@ -13950,7 +13943,7 @@
     </row>
     <row r="940" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A940" s="3" t="s">
-        <v>1924</v>
+        <v>243</v>
       </c>
       <c r="B940" s="3" t="s">
         <v>1657</v>
@@ -13958,7 +13951,7 @@
     </row>
     <row r="941" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A941" s="3" t="s">
-        <v>243</v>
+        <v>1764</v>
       </c>
       <c r="B941" s="3" t="s">
         <v>1658</v>
@@ -13966,7 +13959,7 @@
     </row>
     <row r="942" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A942" s="3" t="s">
-        <v>1765</v>
+        <v>1924</v>
       </c>
       <c r="B942" s="3" t="s">
         <v>1659</v>
@@ -13974,241 +13967,233 @@
     </row>
     <row r="943" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A943" s="3" t="s">
-        <v>1925</v>
+        <v>687</v>
       </c>
       <c r="B943" s="3" t="s">
-        <v>1660</v>
+        <v>696</v>
       </c>
     </row>
     <row r="944" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A944" s="3" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B944" s="3" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A945" s="3" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B945" s="3" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="946" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A946" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B946" s="3" t="s">
-        <v>699</v>
-      </c>
+        <v>700</v>
+      </c>
+      <c r="F946" s="10"/>
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A947" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B947" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="F947" s="10"/>
+        <v>701</v>
+      </c>
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A948" s="3" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B948" s="3" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A949" s="3" t="s">
-        <v>692</v>
+        <v>1925</v>
       </c>
       <c r="B949" s="3" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A950" s="3" t="s">
-        <v>1926</v>
+        <v>693</v>
       </c>
       <c r="B950" s="3" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A951" s="3" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B951" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A952" s="3" t="s">
-        <v>694</v>
+        <v>1660</v>
       </c>
       <c r="B952" s="3" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A953" s="3" t="s">
-        <v>1661</v>
+        <v>695</v>
       </c>
       <c r="B953" s="3" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="954" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A954" s="3" t="s">
-        <v>695</v>
+        <v>708</v>
       </c>
       <c r="B954" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A955" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B955" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A956" s="3" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B956" s="3" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A957" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="B957" s="3" t="s">
-        <v>725</v>
+      <c r="A957" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="B957" s="11" t="s">
+        <v>726</v>
       </c>
     </row>
     <row r="958" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A958" s="11" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B958" s="11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A959" s="11" t="s">
-        <v>716</v>
-      </c>
-      <c r="B959" s="11" t="s">
-        <v>727</v>
+      <c r="A959" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B959" s="3" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A960" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B960" s="3" t="s">
-        <v>718</v>
+        <v>728</v>
       </c>
     </row>
     <row r="961" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A961" s="3" t="s">
-        <v>719</v>
+        <v>1663</v>
       </c>
       <c r="B961" s="3" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="962" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A962" s="3" t="s">
-        <v>1664</v>
+        <v>724</v>
       </c>
       <c r="B962" s="3" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="963" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A963" s="3" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B963" s="3" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="964" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A964" s="3" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B964" s="3" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="965" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A965" s="3" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B965" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="966" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A966" s="3" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B966" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="967" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A967" s="3" t="s">
-        <v>723</v>
+        <v>1662</v>
       </c>
       <c r="B967" s="3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="968" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A968" s="3" t="s">
-        <v>1663</v>
+        <v>736</v>
       </c>
       <c r="B968" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
     <row r="969" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A969" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B969" s="3" t="s">
-        <v>737</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="970" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A970" s="3" t="s">
-        <v>738</v>
+        <v>1661</v>
       </c>
       <c r="B970" s="3" t="s">
-        <v>1520</v>
-      </c>
-    </row>
-    <row r="971" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A971" s="3" t="s">
-        <v>1662</v>
-      </c>
-      <c r="B971" s="3" t="s">
         <v>697</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B971" xr:uid="{7BD56D84-AAB8-4F28-8C6E-523199CE1743}"/>
+  <autoFilter ref="A1:B970" xr:uid="{7BD56D84-AAB8-4F28-8C6E-523199CE1743}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A864:B943 A1 A2:B846 A847:A848 A944:A971">
+  <conditionalFormatting sqref="A863:B942 A1 A2:B845 A846:A847 A943:A970">
     <cfRule type="duplicateValues" dxfId="1" priority="8" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
